--- a/Competition_Action_Plan.xlsx
+++ b/Competition_Action_Plan.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -708,7 +708,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (10%); rival Diagnostic lab 413 vs our 288 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (10%); rival Blood testing service 413 vs our 288 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -824,15 +824,15 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>INVEST ↑</t>
+        <v>18</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>INVEST ↑ (careful)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -842,21 +842,21 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>IS 60% · Loc→Lead 10% · Lead→Book 60% · CPL ₹1279</t>
+          <t>IS 48% · Loc→Lead 43% · Lead→Book 77% · CPL ₹91</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 60%) but map clicks don't convert (10%); rival Diagnostic lab 191 vs our 99 reviews wins the listing. Scale + build reviews.</t>
+          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 64× (21686 vs 338). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Kamatwade (191)</t>
+          <t>Nisarga Diagnostics (21686)</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>99</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
@@ -867,11 +867,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -885,36 +885,36 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>IS 48% · Loc→Lead 43% · Lead→Book 77% · CPL ₹91</t>
+          <t>IS 37% · Loc→Lead 46% · Lead→Book 69% · CPL ₹107</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 64× (21686 vs 338). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>⚠ Google shows room (IS 37%) BUT rival out-reviews us 40× (15414 vs 386). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Nisarga Diagnostics (21686)</t>
+          <t>Infinity Medical Centre - Home Blood test, CT scan, MRI Scan, PET scan, X-ray, DLCO, PFT in Parel (15414)</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>338</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>IS 64% · Loc→Lead 24% · Lead→Book 79% · CPL ₹196</t>
+          <t>IS 48% · Loc→Lead 36% · Lead→Book 72% · CPL ₹138</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Ayurvedic rival (7034 vs 386 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 28× (8968 vs 320). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Dr Yogendra Rai (7034)</t>
+          <t>Indian Scan (8968)</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>386</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
@@ -953,11 +953,11 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -971,60 +971,60 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>IS 52% · Loc→Lead 26% · Lead→Book 74% · CPL ₹274</t>
+          <t>IS 51% · Loc→Lead 36% · Lead→Book 67% · CPL ₹105</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Diagnostic lab rival (7469 vs 329 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>⚠ Google shows room (IS 51%) BUT rival out-reviews us 38× (11472 vs 305). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Panjagutta - Pathology &amp; Radiology Lab | Full Body Checkup (7469)</t>
+          <t>Vijaya PH Diagnostic Centre (11472)</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>329</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>18</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>IS 37% · Loc→Lead 46% · Lead→Book 69% · CPL ₹107</t>
+          <t>IS 29% · Loc→Lead 9% · Lead→Book 47% · CPL ₹400</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 37%) BUT rival out-reviews us 40× (15414 vs 386). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>Room to scale (IS 29%) but map clicks don't convert (9%); rival Hospital 8907 vs our 386 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Infinity Medical Centre - Home Blood test, CT scan, MRI Scan, PET scan, X-ray, DLCO, PFT in Parel (15414)</t>
+          <t>Motherhood Hospital Hebbal, Bangalore - Best Maternity Hospital in Bangalore (8907)</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1039,82 +1039,82 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>17</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>IS 56% · Loc→Lead 22% · Lead→Book 81% · CPL ₹165</t>
+          <t>IS 52% · Loc→Lead 19% · Lead→Book 81% · CPL ₹162</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2242 vs 320 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 385 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>A4 Hospital (2242)</t>
+          <t>Apollo Medical Centre - Marathahalli, Bengaluru (7670)</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>320</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>IS 48% · Loc→Lead 36% · Lead→Book 72% · CPL ₹138</t>
+          <t>IS 57% · Loc→Lead 17% · Lead→Book 76% · CPL ₹223</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 7× (2294 vs 320). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Allopathic 2375 vs our 258 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Hitech Labs | Ultrasound, Radiology &amp; Pathology Lab in T. Nagar (2294)</t>
+          <t>Androcare Andrology Institute (2375)</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
@@ -1125,39 +1125,39 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>12</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>IS 65% · Loc→Lead 20% · Lead→Book 82% · CPL ₹186</t>
+          <t>IS 64% · Loc→Lead 24% · Lead→Book 79% · CPL ₹196</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2139 vs 305 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Ayurvedic rival (7034 vs 386 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Kidney And Urology Super Speciality Institute Hospital (2139)</t>
+          <t>Dr Yogendra Rai (7034)</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>305</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
@@ -1168,39 +1168,39 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>12</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>IS 51% · Loc→Lead 36% · Lead→Book 67% · CPL ₹105</t>
+          <t>IS 52% · Loc→Lead 26% · Lead→Book 74% · CPL ₹274</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 51%) BUT rival out-reviews us 16× (4987 vs 305). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>Map clicks leak — listing loses to Diagnostic center rival (13163 vs 329 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Dr Tayades Pathlab Diagnostic Center (4987)</t>
+          <t>Vijaya Diagnostic Centre A.S. Rao Nagar - Pathology &amp; Radiology Lab | Full Body Checkup (13163)</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>305</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
@@ -1211,54 +1211,54 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+        <v>8</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>IS 58% · Loc→Lead 22% · Lead→Book 76% · CPL ₹178</t>
+          <t>IS 56% · Loc→Lead 22% · Lead→Book 81% · CPL ₹165</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (875 vs 41 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (2242 vs 320 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Dr. M Prasada Rao (875)</t>
+          <t>A4 Hospital (2242)</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>41</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -1267,41 +1267,41 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>IS 29% · Loc→Lead 9% · Lead→Book 47% · CPL ₹400</t>
+          <t>IS 65% · Loc→Lead 20% · Lead→Book 82% · CPL ₹186</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 29%) but map clicks don't convert (9%); rival Hospital / Psych hospital 8907 vs our 386 reviews wins the listing. Scale + build reviews.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (2139 vs 305 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Motherhood Hospital Hebbal, Bangalore - Best Maternity Hospital in Bangalore (8907)</t>
+          <t>Kidney And Urology Super Speciality Institute Hospital (2139)</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>386</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
@@ -1310,26 +1310,26 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>IS 52% · Loc→Lead 19% · Lead→Book 81% · CPL ₹162</t>
+          <t>IS 36% · Loc→Lead 10% · Lead→Book 52% · CPL ₹266</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 385 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 36%) but map clicks don't convert (10%); rival Hospital 11251 vs our 305 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Apollo Medical Centre - Marathahalli, Bengaluru (7670)</t>
+          <t>Noble Hospitals &amp; Research Centre (11251)</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>385</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -1353,41 +1353,41 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>IS 57% · Loc→Lead 17% · Lead→Book 76% · CPL ₹223</t>
+          <t>IS 46% · Loc→Lead 9% · Lead→Book 78% · CPL ₹204</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Allopathic 2375 vs our 258 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 15776 vs our 29 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Androcare Andrology Institute (2375)</t>
+          <t>GIPS Hospital and De-addiction Centre (15776)</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>258</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Amravati</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
@@ -1396,26 +1396,26 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>IS 36% · Loc→Lead 10% · Lead→Book 52% · CPL ₹266</t>
+          <t>IS 73% · Loc→Lead 5% · Lead→Book 67% · CPL ₹1070</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 36%) but map clicks don't convert (10%); rival Hospital / Psych hospital 11251 vs our 305 reviews wins the listing. Scale + build reviews.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (992 vs 3 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Noble Hospitals &amp; Research Centre (11251)</t>
+          <t>𝗦𝗮𝗺𝗮𝗿𝘁𝗵 𝗦𝘂𝗽𝗲𝗿 -Specialty Heart Hospital-Cardiologist/Heart Specialist/Physician/Best Hospital in Amravati (992)</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>305</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -1439,26 +1439,26 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>IS 46% · Loc→Lead 9% · Lead→Book 78% · CPL ₹204</t>
+          <t>IS 55% · Loc→Lead 18% · Lead→Book 73% · CPL ₹112</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 15776 vs our 29 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Allopathic 3253 vs our 288 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>GIPS Hospital and De-addiction Centre (15776)</t>
+          <t>Vazhikatti Mental Health Centre &amp; Research Institute (3253)</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1482,26 +1482,26 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>IS 73% · Loc→Lead 5% · Lead→Book 67% · CPL ₹1070</t>
+          <t>IS 52% · Loc→Lead 12% · Lead→Book 71% · CPL ₹239</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (992 vs 3 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Allopathic 196 vs our 15 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>𝗦𝗮𝗺𝗮𝗿𝘁𝗵 𝗦𝘂𝗽𝗲𝗿 -Specialty Heart Hospital-Cardiologist/Heart Specialist/Physician/Best Hospital in Amravati (992)</t>
+          <t>Navkar Clinic &amp; Health Care (196)</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Hubli</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -1525,26 +1525,26 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>IS 55% · Loc→Lead 18% · Lead→Book 73% · CPL ₹112</t>
+          <t>IS 63% · Loc→Lead 19% · Lead→Book 68% · CPL ₹217</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Allopathic 3253 vs our 288 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1207 vs our 31 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Vazhikatti Mental Health Centre &amp; Research Institute (3253)</t>
+          <t>Dr Shambhu K MBBS, MS, MCh, F MAS Urologist &amp; Andrologist, Laparoscopic &amp; Transplant Surgeon (1207)</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>288</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -1568,26 +1568,26 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>IS 52% · Loc→Lead 12% · Lead→Book 71% · CPL ₹239</t>
+          <t>IS 45% · Loc→Lead 14% · Lead→Book 52% · CPL ₹228</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Allopathic 196 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 536 vs our 90 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Navkar Clinic &amp; Health Care (196)</t>
+          <t>Dr. Kapil Sharma - Best Psychiatrist in Jaipur | Best Psychologist in Jaipur (536)</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hubli</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -1611,26 +1611,26 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>IS 63% · Loc→Lead 19% · Lead→Book 68% · CPL ₹217</t>
+          <t>IS 57% · Loc→Lead 10% · Lead→Book 82% · CPL ₹270</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1207 vs our 31 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1565 vs our 179 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Dr Shambhu K MBBS, MS, MCh, F MAS Urologist &amp; Andrologist, Laparoscopic &amp; Transplant Surgeon (1207)</t>
+          <t>Krisham Men's Health (Sexology) And Diabetis Clinic (1565)</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>31</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1654,26 +1654,26 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>IS 45% · Loc→Lead 14% · Lead→Book 52% · CPL ₹228</t>
+          <t>IS 54% · Loc→Lead 8% · Lead→Book 64% · CPL ₹479</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 536 vs our 90 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 535 vs our 2 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kapil Sharma - Best Psychiatrist in Jaipur | Best Psychologist in Jaipur (536)</t>
+          <t>Skinroots (535)</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
@@ -1697,26 +1697,26 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>IS 57% · Loc→Lead 10% · Lead→Book 82% · CPL ₹270</t>
+          <t>IS 57% · Loc→Lead 1% · Lead→Book 100% · CPL ₹3231</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1565 vs our 179 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (1%); rival Allopathic 1479 vs our 0 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Krisham Men's Health (Sexology) And Diabetis Clinic (1565)</t>
+          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -1740,26 +1740,26 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>IS 54% · Loc→Lead 8% · Lead→Book 64% · CPL ₹479</t>
+          <t>IS 58% · Loc→Lead 12% · Lead→Book 63% · CPL ₹134</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 535 vs our 2 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Ayurvedic 706 vs our 33 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Skinroots (535)</t>
+          <t>Kalptaru Ayurvedam (706)</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -1783,37 +1783,37 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>IS 57% · Loc→Lead 1% · Lead→Book 100% · CPL ₹3231</t>
+          <t>IS 58% · Loc→Lead 22% · Lead→Book 76% · CPL ₹178</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (1%); rival Allopathic 1479 vs our 0 reviews wins the listing. Scale + build reviews.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (875 vs 41 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
+          <t>Dr. M Prasada Rao (875)</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Hubli</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -1826,26 +1826,26 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>IS 58% · Loc→Lead 12% · Lead→Book 63% · CPL ₹134</t>
+          <t>IS 61% · Loc→Lead 17% · Lead→Book 50% · CPL ₹1052</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Ayurvedic 706 vs our 33 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 61%) but map clicks don't convert (17%); rival Doctor 635 vs our 31 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Kalptaru Ayurvedam (706)</t>
+          <t>Dr Chetan K Ganteppanavar - Consultant Physician and Diabetologist - Kalpana Multispeciality Clinic Hubli, India (635)</t>
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Hubli</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
@@ -1869,26 +1869,26 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>IS 61% · Loc→Lead 17% · Lead→Book 50% · CPL ₹1052</t>
+          <t>IS 51% · Loc→Lead 6% · Lead→Book 25% · CPL ₹893</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 61%) but map clicks don't convert (17%); rival STD/HIV clinic 585 vs our 31 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 51%) but map clicks don't convert (6%); rival Sexologist 1566 vs our 179 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>JEEVANNAVAR SKIN CARE CLINIC (585)</t>
+          <t>Krisham Men's Health (Sexology) And Diabetis Clinic (1566)</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>31</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -1912,26 +1912,26 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>IS 51% · Loc→Lead 6% · Lead→Book 25% · CPL ₹893</t>
+          <t>IS 60% · Loc→Lead 10% · Lead→Book 60% · CPL ₹1279</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 51%) but map clicks don't convert (6%); rival Diagnostic lab 1036 vs our 179 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 60%) but map clicks don't convert (10%); rival Medical clinic 4937 vs our 99 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs (1036)</t>
+          <t>Unique Multicare Clinic (4937)</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>179</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 47%) but map clicks don't convert (10%); rival Hospital / Clinic 870 vs our 33 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 47%) but map clicks don't convert (10%); rival HIV testing center 1162 vs our 33 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Naveli Hospital | Dr Keyur Yagnik | Dr Reshma Yagnik | Bariatric Surgeon | Hernia Surgeon (870)</t>
+          <t>IID Hospital - Institute of Infectious Diseases (1162)</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 62%) but map clicks don't convert (15%); rival Diagnostic lab 225 vs our 41 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 62%) but map clicks don't convert (15%); rival Specialized clinic 567 vs our 41 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Home Collection Lab (BLOOD TESTING SERVICE) (225)</t>
+          <t>Dr.MEGHANATH YENNI MD;DNB (567)</t>
         </is>
       </c>
       <c r="I34" s="4" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Santasa Fertility &amp; IVF, Mysore (201)</t>
+          <t>Apollo Clinic (4866)</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 48%) but map clicks don't convert (9%); rival Hospital / Psych hospital 2542 vs our 260 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 48%) but map clicks don't convert (9%); rival Hospital 2542 vs our 260 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 53%) but map clicks don't convert (5%); rival Diagnostic lab 3455 vs our 29 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 53%) but map clicks don't convert (5%); rival Psychiatrist 15775 vs our 29 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Redcliffe Labs - Ahmedabad | Full Body Checkup in Ahmedabad (3455)</t>
+          <t>GIPS Hospital and De-addiction Centre (15775)</t>
         </is>
       </c>
       <c r="I44" s="4" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Diagnostic lab rival (613 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Pathologist rival (613 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 47%) but map clicks don't convert (15%); rival Diagnostic lab 641 vs our 16 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 47%) but map clicks don't convert (15%); rival Sexologist 1078 vs our 16 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs (641)</t>
+          <t>Dr Diwakar's Clinic (1078)</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 46%) but map clicks don't convert (10%); rival Diagnostic lab 162 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 46%) but map clicks don't convert (10%); rival General hospital 567 vs our 15 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Healthcare Ltd (162)</t>
+          <t>GMERS Civil Hospital (567)</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 50%) but map clicks don't convert (12%); rival Diagnostic lab 1096 vs our 90 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 50%) but map clicks don't convert (12%); rival Diagnostic center 1096 vs our 90 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (18%); rival Hospital / Clinic 111 vs our 168 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (18%); rival Diagnostic center 785 vs our 168 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>w centre for sexual wellness (111)</t>
+          <t>Sparsha Diagnostics (785)</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 7/12 clinics out-reviewed (top rival Dr Sagar Mundada 788 vs our median 386).</t>
+          <t>No paid spend. 9/12 clinics out-reviewed (top rival Growth Centre India Private Limited 1833 vs our median 386).</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Dr Sagar Mundada (788)</t>
+          <t>Growth Centre India Private Limited (1833)</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 7/8 clinics out-reviewed (top rival Apollo Clinic - Velachery, Chennai 5650 vs our median 320).</t>
+          <t>No paid spend. 8/8 clinics out-reviewed (top rival Apollo Clinic - Velachery, Chennai 5650 vs our median 320).</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore 720 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1517 vs our median 1).</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore (720)</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1517)</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore 720 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1517 vs our median 1).</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore (720)</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1517)</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Unique Diagnostic Centre 1202 vs our median 380).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup 18578 vs our median 12).</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -3260,11 +3260,11 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Unique Diagnostic Centre (1202)</t>
+          <t>Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup (18578)</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>380</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pathkind Labs 640 vs our median 2).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Unique Diagnostic Centre 1202 vs our median 380).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3303,11 +3303,11 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs (640)</t>
+          <t>Unique Diagnostic Centre (1202)</t>
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Metropolis Labs | Blood Test &amp; Diagnostic Centre in Rajkot 633 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pathkind Labs 640 vs our median 2).</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Rajkot (633)</t>
+          <t>Pathkind Labs (640)</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Krsnaa Diagnostics | Blood Test &amp; Diagnostic Centre In Ranchi 404 vs our median 392).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bhatt Pathology Laboratory - Main Branch 5653 vs our median 0).</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3389,11 +3389,11 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Krsnaa Diagnostics | Blood Test &amp; Diagnostic Centre In Ranchi (404)</t>
+          <t>Dr. Bhatt Pathology Laboratory - Main Branch (5653)</t>
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Tumkur</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Indira IVF Fertility Centre in Tumkur - Best IVF Centre 156 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Health Home 761 vs our median 392).</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -3432,11 +3432,11 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Indira IVF Fertility Centre in Tumkur - Best IVF Centre (156)</t>
+          <t>Health Home (761)</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Tumkur</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Devarsh Surgical &amp; Maternity Hospital 481 vs our median 15).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Indira IVF Fertility Centre in Tumkur - Best IVF Centre 156 vs our median 0).</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Devarsh Surgical &amp; Maternity Hospital (481)</t>
+          <t>Indira IVF Fertility Centre in Tumkur - Best IVF Centre (156)</t>
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival GIPS Hospital and De-addiction Centre 15776 vs our median 29).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1497 vs our median 15).</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -3518,11 +3518,11 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>GIPS Hospital and De-addiction Centre (15776)</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1497)</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Mauli Neurocare and Neurosurgery Hospital 256 vs our median 3).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival GIPS Hospital and De-addiction Centre 15776 vs our median 29).</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3561,11 +3561,11 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Mauli Neurocare and Neurosurgery Hospital (256)</t>
+          <t>GIPS Hospital and De-addiction Centre (15776)</t>
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Aurangabad</t>
+          <t>Amravati</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad 1237 vs our median 53).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vertex Healing Centre 483 vs our median 3).</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3604,11 +3604,11 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad (1237)</t>
+          <t>Vertex Healing Centre (483)</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Aurangabad</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार 1451 vs our median 16).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad 1237 vs our median 53).</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार (1451)</t>
+          <t>Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad (1237)</t>
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival SMVS Swaminarayan Hospital 15626 vs our median 15).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार 1451 vs our median 16).</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>SMVS Swaminarayan Hospital (15626)</t>
+          <t>Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार (1451)</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore 352 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival SMVS Swaminarayan Hospital 15626 vs our median 15).</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -3733,11 +3733,11 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore (352)</t>
+          <t>SMVS Swaminarayan Hospital (15626)</t>
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore 352 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore (352)</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival YASH Relationship Centre (Lenin Perumalla Psychologist) 572 vs our median 12).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -3819,11 +3819,11 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>YASH Relationship Centre (Lenin Perumalla Psychologist) (572)</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai 624 vs our median 380).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival YASH Relationship Centre (Lenin Perumalla Psychologist) 572 vs our median 12).</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai (624)</t>
+          <t>YASH Relationship Centre (Lenin Perumalla Psychologist) (572)</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>380</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Krithishree S S 254 vs our median 168).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai 624 vs our median 380).</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -3905,11 +3905,11 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Dr Krithishree S S (254)</t>
+          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai (624)</t>
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>168</v>
+        <v>380</v>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Sourabh Pal 592 vs our median 179).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka 1244 vs our median 168).</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3948,11 +3948,11 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Dr. Sourabh Pal (592)</t>
+          <t>Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka (1244)</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Hemant Sonanis - Best Psychiatrist and Counselor in Nashik 495 vs our median 99).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Sourabh Pal 592 vs our median 179).</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3991,11 +3991,11 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Dr. Hemant Sonanis - Best Psychiatrist and Counselor in Nashik (495)</t>
+          <t>Dr. Sourabh Pal (592)</t>
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>99</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bakhru's 2214 vs our median 2).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik 1382 vs our median 99).</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -4034,11 +4034,11 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Dr. Bakhru's (2214)</t>
+          <t>Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik (1382)</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot 1479 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bakhru's 2214 vs our median 2).</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -4077,11 +4077,11 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
+          <t>Dr. Bakhru's (2214)</t>
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Ravish Ranjan 586 vs our median 392).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot 1479 vs our median 0).</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -4120,11 +4120,11 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Dr. Ravish Ranjan (586)</t>
+          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Mayank Agrawal 520 vs our median 33).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Paramarsh Bharti 994 vs our median 392).</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Dr. Mayank Agrawal (520)</t>
+          <t>Paramarsh Bharti (994)</t>
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>33</v>
+        <v>392</v>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Tumkur</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Siddaganga Medical College &amp; Research Institute 1139 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Best Career Counselling 948 vs our median 33).</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -4206,11 +4206,11 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Siddaganga Medical College &amp; Research Institute (1139)</t>
+          <t>Best Career Counselling (948)</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Tumkur</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC 1150 vs our median 15).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Siddaganga Medical College &amp; Research Institute 1139 vs our median 0).</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4249,11 +4249,11 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC (1150)</t>
+          <t>Siddaganga Medical College &amp; Research Institute (1139)</t>
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr G.SURESH KUMAR 680 vs our median 41).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC 1150 vs our median 15).</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
@@ -4292,10 +4292,53 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>Dr G.SURESH KUMAR (680)</t>
+          <t>Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC (1150)</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Mental Health</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>ORGANIC</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Reviews / GMB</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag 720 vs our median 41).</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag (720)</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="n">
         <v>41</v>
       </c>
     </row>
@@ -4443,7 +4486,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>IS 61% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>IS 61% room, gap 2.5× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4528,12 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>IS 68% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Gap coverable (0.6×) + IS 68% room — bid/profile push can win the click while reviews catch up</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4575,12 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>IS 52% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Gap coverable (1.4×) + IS 52% room — bid/profile push can win the click while reviews catch up</t>
         </is>
       </c>
     </row>
@@ -4579,64 +4622,66 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
+          <t>Bid / Budget ↑</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Gap coverable (1.5×) + IS 69% room — bid/profile push can win the click while reviews catch up</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>INVEST ↑ (careful)  ·  FEED THIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>INVEST ↑ (careful)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>STI</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>4141</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>21686 vs 338 (64×)</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
           <t>Budget / Bid + Reviews</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>IS 69% room, funnel OK — raise budget/bid + build reviews</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>INVEST ↑</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>STI</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Nashik</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>1066</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>191 vs 99 (2×)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Budget / Bid + Reviews</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>IS 60% room, funnel OK — raise budget/bid + build reviews</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)  ·  FEED THIS</t>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>IS 48% room, gap 64.2× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4648,32 +4693,32 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>14490</v>
+        <v>2440</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.203</v>
+        <v>0.475</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.361</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.82</v>
+        <v>0.717</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>302</v>
+        <v>244</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>2139 vs 305 (7×)</t>
+          <t>8968 vs 320 (28×)</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -4683,7 +4728,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>IS 65% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>IS 48% room, gap 28.0× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4740,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4704,23 +4749,23 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>13395</v>
+        <v>1856</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.238</v>
+        <v>0.374</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.464</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.788</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>335</v>
+        <v>186</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>7034 vs 386 (18×)</t>
+          <t>15414 vs 386 (40×)</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -4730,7 +4775,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>IS 64% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>IS 37% room, gap 39.9× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4742,32 +4787,32 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>9365</v>
+        <v>1697</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.223</v>
+        <v>0.512</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.362</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.806</v>
+        <v>0.67</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2242 vs 320 (7×)</t>
+          <t>11472 vs 305 (38×)</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -4777,66 +4822,26 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>IS 56% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>IS 51% room, gap 37.6× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>STI</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>4836</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>403</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>7469 vs 329 (23×)</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Budget / Bid + Reviews</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>IS 52% room, funnel OK — raise budget/bid + build reviews</t>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST  ·  FIX BEFORE SCALING</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>INVEST ↑ (careful)</t>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4845,228 +4850,268 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>4141</v>
+        <v>18486</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>0.432</v>
+        <v>0.523</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.191</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.766</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>143</v>
+        <v>272</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>21686 vs 338 (64×)</t>
+          <t>7670 vs 385 (20×)</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>IS 48% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Rival out-reviews us 20× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>INVEST ↑ (careful)</t>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>2440</v>
+        <v>16053</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>0.361</v>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.169</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.717</v>
+        <v>0.762</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>244</v>
+        <v>401</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>2294 vs 320 (7×)</t>
+          <t>2375 vs 258 (9×)</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>IS 48% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Rival out-reviews us 9× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>INVEST ↑ (careful)</t>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>1856</v>
+        <v>14490</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>0.464</v>
+        <v>0.652</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.203</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>15414 vs 386 (40×)</t>
+          <t>2139 vs 305 (7×)</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>IS 37% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Rival out-reviews us 7× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>INVEST ↑ (careful)</t>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1697</v>
+        <v>13395</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>0.362</v>
+        <v>0.645</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.238</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.67</v>
+        <v>0.788</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>212</v>
+        <v>335</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>4987 vs 305 (16×)</t>
+          <t>7034 vs 386 (18×)</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>IS 51% room, funnel OK — raise budget/bid + build reviews</t>
+          <t>Rival out-reviews us 18× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>INVEST ↑ (careful)</t>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>Mental Health</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>9876</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>1975</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>8907 vs 386 (23×)</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Reviews (not bid)</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Rival out-reviews us 23× — too heavy to win on ads; build reviews, don't push bid here</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Sexual Health</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Visakhapatnam</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>1575</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>394</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>875 vs 41 (21×)</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Budget / Bid + Reviews</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>IS 58% room, funnel OK — raise budget/bid + build reviews</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>FIX PROFILE FIRST  ·  FIX BEFORE SCALING</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>9365</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>268</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>2242 vs 320 (7×)</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Reviews (not bid)</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Rival out-reviews us 7× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5078,42 +5123,42 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>18486</v>
+        <v>4836</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>0.191</v>
+        <v>0.515</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>0.26</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.736</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>272</v>
+        <v>403</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>7670 vs 385 (20×)</t>
+          <t>13163 vs 329 (40×)</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 19% &amp; rival out-reviews 20× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 40× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5125,42 +5170,42 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>16053</v>
+        <v>4064</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>0.762</v>
+        <v>0.077</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>0.555</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>401</v>
+        <v>677</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>2375 vs 258 (9×)</t>
+          <t>3253 vs 288 (11×)</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 17% &amp; rival out-reviews 9× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 11× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5172,42 +5217,42 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9876</v>
+        <v>2925</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0.288</v>
+        <v>0.453</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>0.093</v>
+        <v>0.139</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.466</v>
+        <v>0.519</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>1975</v>
+        <v>975</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>8907 vs 386 (23×)</t>
+          <t>536 vs 90 (6×)</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 9% &amp; rival out-reviews 23× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 6× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5224,37 +5269,37 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>4064</v>
+        <v>2754</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.219</v>
+        <v>0.355</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.077</v>
+        <v>0.095</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.555</v>
+        <v>0.516</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>3253 vs 288 (11×)</t>
+          <t>11251 vs 305 (37×)</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 8% &amp; rival out-reviews 11× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 37× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5271,37 +5316,37 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>2925</v>
+        <v>2721</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>0.519</v>
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0.775</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>975</v>
+        <v>454</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>536 vs 90 (6×)</t>
+          <t>15776 vs 29 (544×)</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 14% &amp; rival out-reviews 6× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 544× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5313,42 +5358,42 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2754</v>
+        <v>2522</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.355</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>0.516</v>
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>0.821</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>688</v>
+        <v>504</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>11251 vs 305 (37×)</t>
+          <t>1565 vs 179 (9×)</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 10% &amp; rival out-reviews 37× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 9× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5365,37 +5410,37 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>2721</v>
+        <v>2190</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>0.456</v>
+        <v>0.521</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.775</v>
+        <v>0.709</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>454</v>
+        <v>548</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>15776 vs 29 (544×)</t>
+          <t>196 vs 15 (13×)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 9% &amp; rival out-reviews 544× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 13× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5412,37 +5457,37 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>2522</v>
+        <v>1854</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>0.821</v>
+        <v>0.12</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>0.627</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>504</v>
+        <v>371</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>1565 vs 179 (9×)</t>
+          <t>706 vs 33 (21×)</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 10% &amp; rival out-reviews 9× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 21× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5459,37 +5504,37 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>2190</v>
+        <v>1752</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.521</v>
+        <v>0.547</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>0.123</v>
+        <v>0.178</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.709</v>
+        <v>0.734</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>548</v>
+        <v>250</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>196 vs 15 (13×)</t>
+          <t>3253 vs 288 (11×)</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 12% &amp; rival out-reviews 13× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 11× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5506,37 +5551,37 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1854</v>
+        <v>1575</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>0.627</v>
+        <v>0.583</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0.755</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>706 vs 33 (21×)</t>
+          <t>875 vs 41 (21×)</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 12% &amp; rival out-reviews 21× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 21× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5548,42 +5593,40 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>1752</v>
+        <v>1191</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.547</v>
+        <v>0.511</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="G30" s="17" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>250</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>3253 vs 288 (11×)</t>
+          <t>1566 vs 179 (9×)</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 18% &amp; rival out-reviews 11× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 9× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5595,40 +5638,40 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Sexual Health</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1191</v>
+        <v>1117</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.511</v>
+        <v>0.535</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.25</v>
+        <v>0.643</v>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>1036 vs 179 (6×)</t>
+          <t>535 vs 2 (268×)</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 6% &amp; rival out-reviews 6× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 268× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5645,35 +5688,35 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Amravati</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>1117</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.535</v>
+        <v>1070</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0.734</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>0.643</v>
+        <v>0.052</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0.667</v>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>535 vs 2 (268×)</t>
+          <t>992 vs 3 (331×)</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 8% &amp; rival out-reviews 268× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 331× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5685,40 +5728,40 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Sexual Health</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.734</v>
+        <v>1066</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.6</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>0.667</v>
+        <v>0.104</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>0.6</v>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>992 vs 3 (331×)</t>
+          <t>4937 vs 99 (50×)</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 5% &amp; rival out-reviews 331× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 50× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5801,12 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 4% &amp; rival out-reviews 30× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 30× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5848,12 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 19% &amp; rival out-reviews 39× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 39× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5845,17 +5888,17 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>870 vs 33 (26×)</t>
+          <t>1162 vs 33 (35×)</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 10% &amp; rival out-reviews 26× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 35× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5890,17 +5933,17 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>225 vs 41 (5×)</t>
+          <t>567 vs 41 (14×)</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 15% &amp; rival out-reviews 5× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 14× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5983,12 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 1% &amp; rival out-reviews 99× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 99× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5980,17 +6023,17 @@
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>585 vs 31 (19×)</t>
+          <t>635 vs 31 (20×)</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Loc→Lead 17% &amp; rival out-reviews 19× — paid leaks to them; build reviews before scaling</t>
+          <t>Rival out-reviews us 20× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6178,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>201 vs 550 (0×)</t>
+          <t>4866 vs 550 (9×)</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
@@ -6377,7 +6420,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>3455 vs 29 (119×)</t>
+          <t>15775 vs 29 (544×)</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
@@ -6471,7 +6514,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>162 vs 15 (11×)</t>
+          <t>567 vs 15 (38×)</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
@@ -6565,7 +6608,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>111 vs 168 (1×)</t>
+          <t>785 vs 168 (5×)</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
@@ -6612,7 +6655,7 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>641 vs 16 (40×)</t>
+          <t>1078 vs 16 (67×)</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -6732,11 +6775,11 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6892,7 +6935,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E3" s="15" t="n">
@@ -6963,7 +7006,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
@@ -7027,14 +7070,14 @@
       <c r="B5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E5" s="15" t="n">
@@ -7098,14 +7141,14 @@
       <c r="B6" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E6" s="15" t="n">
@@ -7169,14 +7212,14 @@
       <c r="B7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E7" s="15" t="n">
@@ -7318,7 +7361,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E9" s="15" t="n">
@@ -7389,7 +7432,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
@@ -7460,7 +7503,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E11" s="15" t="n">
@@ -7602,7 +7645,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E13" s="15" t="n">
@@ -7673,7 +7716,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
@@ -7815,7 +7858,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E16" s="15" t="n">
@@ -7886,7 +7929,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E17" s="15" t="n">
@@ -7950,14 +7993,14 @@
       <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E18" s="15" t="n">
@@ -8028,7 +8071,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
@@ -8170,7 +8213,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
@@ -8241,7 +8284,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
@@ -8383,7 +8426,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
@@ -8525,7 +8568,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
@@ -9070,14 +9113,14 @@
       <c r="B3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>INVEST ↑ (careful)</t>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E3" s="15" t="n">
@@ -9109,26 +9152,26 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Panjagutta - Pathology &amp; Radiology Lab | Full Body Checkup</t>
+          <t>Vijaya Diagnostic Centre A.S. Rao Nagar - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P3" s="4" t="n">
-        <v>7469</v>
+        <v>13163</v>
       </c>
       <c r="Q3" s="26" t="n">
-        <v>22.7</v>
+        <v>40</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Diagnostic lab rival (7469 vs 329 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Diagnostic center rival (13163 vs 329 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9228,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P4" s="4" t="n">
@@ -9251,26 +9294,26 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Hitech Labs | Ultrasound, Radiology &amp; Pathology Lab in T. Nagar</t>
+          <t>Indian Scan</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P5" s="4" t="n">
-        <v>2294</v>
+        <v>8968</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 7× (2294 vs 320). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>⚠ Google shows room (IS 48%) BUT rival out-reviews us 28× (8968 vs 320). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9370,7 @@
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P6" s="4" t="n">
@@ -9341,7 +9384,7 @@
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 50%) but map clicks don't convert (12%); rival Diagnostic lab 1096 vs our 90 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 50%) but map clicks don't convert (12%); rival Diagnostic center 1096 vs our 90 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9441,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>STD testing service</t>
         </is>
       </c>
       <c r="P7" s="4" t="n">
@@ -9469,7 +9512,7 @@
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P8" s="4" t="n">
@@ -9535,26 +9578,26 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>Dr Tayades Pathlab Diagnostic Center</t>
+          <t>Vijaya PH Diagnostic Centre</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4987</v>
+        <v>11472</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>16.4</v>
+        <v>37.6</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>⚠ Google shows room (IS 51%) BUT rival out-reviews us 16× (4987 vs 305). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
+          <t>⚠ Google shows room (IS 51%) BUT rival out-reviews us 38× (11472 vs 305). Scaling paid spend leaks to the better-reviewed rival — fix reviews alongside.</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9617,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Bid / Budget ↑</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
@@ -9611,7 +9654,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Blood testing service</t>
         </is>
       </c>
       <c r="P10" s="4" t="n">
@@ -9625,7 +9668,7 @@
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (10%); rival Diagnostic lab 413 vs our 288 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (10%); rival Blood testing service 413 vs our 288 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9677,26 +9720,26 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>Redcliffe Labs - Ahmedabad | Full Body Checkup in Ahmedabad</t>
+          <t>GIPS Hospital and De-addiction Centre</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Psychiatrist</t>
         </is>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3455</v>
+        <v>15775</v>
       </c>
       <c r="Q11" s="26" t="n">
-        <v>119.1</v>
+        <v>544</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 53%) but map clicks don't convert (5%); rival Diagnostic lab 3455 vs our 29 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 53%) but map clicks don't convert (5%); rival Psychiatrist 15775 vs our 29 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9748,26 +9791,26 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Healthcare Ltd</t>
+          <t>GMERS Civil Hospital</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>General hospital</t>
         </is>
       </c>
       <c r="P12" s="4" t="n">
-        <v>162</v>
+        <v>567</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>10.8</v>
+        <v>37.8</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 46%) but map clicks don't convert (10%); rival Diagnostic lab 162 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 46%) but map clicks don't convert (10%); rival General hospital 567 vs our 15 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9830,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E13" s="15" t="n">
@@ -9819,26 +9862,26 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs</t>
+          <t>Krisham Men's Health (Sexology) And Diabetis Clinic</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1036</v>
+        <v>1566</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 51%) but map clicks don't convert (6%); rival Diagnostic lab 1036 vs our 179 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 51%) but map clicks don't convert (6%); rival Sexologist 1566 vs our 179 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9851,14 +9894,14 @@
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>INVEST ↑</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Budget / Bid + Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
@@ -9890,26 +9933,26 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Kamatwade</t>
+          <t>Unique Multicare Clinic</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="Q14" s="27" t="n">
-        <v>1.9</v>
+        <v>4937</v>
+      </c>
+      <c r="Q14" s="26" t="n">
+        <v>49.9</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 60%) but map clicks don't convert (10%); rival Diagnostic lab 191 vs our 99 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 60%) but map clicks don't convert (10%); rival Medical clinic 4937 vs our 99 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -9961,22 +10004,22 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>Santasa Fertility &amp; IVF, Mysore</t>
+          <t>Apollo Clinic</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0.4</v>
+        <v>4866</v>
+      </c>
+      <c r="Q15" s="26" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
@@ -10000,7 +10043,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E16" s="15" t="n">
@@ -10032,26 +10075,26 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Naveli Hospital | Dr Keyur Yagnik | Dr Reshma Yagnik | Bariatric Surgeon | Hernia Surgeon</t>
+          <t>IID Hospital - Institute of Infectious Diseases</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>HIV testing center</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
-        <v>870</v>
+        <v>1162</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>26.4</v>
+        <v>35.2</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 47%) but map clicks don't convert (10%); rival Hospital / Clinic 870 vs our 33 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 47%) but map clicks don't convert (10%); rival HIV testing center 1162 vs our 33 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -10103,26 +10146,26 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>w centre for sexual wellness</t>
+          <t>Sparsha Diagnostics</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0.7</v>
+        <v>785</v>
+      </c>
+      <c r="Q17" s="26" t="n">
+        <v>4.7</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (18%); rival Hospital / Clinic 111 vs our 168 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (18%); rival Diagnostic center 785 vs our 168 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -10174,26 +10217,26 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs</t>
+          <t>Dr Diwakar's Clinic</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
-        <v>641</v>
+        <v>1078</v>
       </c>
       <c r="Q18" s="26" t="n">
-        <v>40.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 47%) but map clicks don't convert (15%); rival Diagnostic lab 641 vs our 16 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 47%) but map clicks don't convert (15%); rival Sexologist 1078 vs our 16 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10256,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
@@ -10245,26 +10288,26 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Home Collection Lab (BLOOD TESTING SERVICE)</t>
+          <t>Dr.MEGHANATH YENNI MD;DNB</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Specialized clinic</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
-        <v>225</v>
+        <v>567</v>
       </c>
       <c r="Q19" s="26" t="n">
-        <v>5.5</v>
+        <v>13.8</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 62%) but map clicks don't convert (15%); rival Diagnostic lab 225 vs our 41 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 62%) but map clicks don't convert (15%); rival Specialized clinic 567 vs our 41 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10364,7 @@
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Pathologist</t>
         </is>
       </c>
       <c r="P20" s="4" t="n">
@@ -10335,7 +10378,7 @@
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Diagnostic lab rival (613 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Pathologist rival (613 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10398,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
@@ -10387,26 +10430,26 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>JEEVANNAVAR SKIN CARE CLINIC</t>
+          <t>Dr Chetan K Ganteppanavar - Consultant Physician and Diabetologist - Kalpana Multispeciality Clinic Hubli, India</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>STD/HIV clinic</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>585</v>
+        <v>635</v>
       </c>
       <c r="Q21" s="26" t="n">
-        <v>18.9</v>
+        <v>20.5</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 61%) but map clicks don't convert (17%); rival STD/HIV clinic 585 vs our 31 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 61%) but map clicks don't convert (17%); rival Doctor 635 vs our 31 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10506,7 @@
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="P22" s="4" t="n">
@@ -10529,19 +10572,19 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="P23" s="4" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="Q23" s="26" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="R23" s="4" t="n">
         <v>1</v>
@@ -10600,19 +10643,19 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="P24" s="4" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="R24" s="4" t="n">
         <v>1</v>
@@ -10671,26 +10714,26 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Apollo 24|7 Lab Tests Near Me | Sree Rama Nagar | Home collection | Kurnool</t>
+          <t>Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>0.5</v>
+        <v>18578</v>
+      </c>
+      <c r="Q25" s="26" t="n">
+        <v>1548.2</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>Holding on reviews organically.</t>
+          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10774,7 @@
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Blood testing service</t>
         </is>
       </c>
       <c r="P26" s="4" t="n">
@@ -10802,7 +10845,7 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P27" s="4" t="n">
@@ -10868,16 +10911,16 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Rajkot</t>
+          <t>Dr. Bhatt Pathology Laboratory - Main Branch</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="P28" s="4" t="n">
-        <v>633</v>
+        <v>5653</v>
       </c>
       <c r="Q28" s="26" t="n">
         <v>99</v>
@@ -10939,19 +10982,19 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Krsnaa Diagnostics | Blood Test &amp; Diagnostic Centre In Ranchi</t>
+          <t>Health Home</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="P29" s="4" t="n">
-        <v>404</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>1</v>
+        <v>761</v>
+      </c>
+      <c r="Q29" s="27" t="n">
+        <v>1.9</v>
       </c>
       <c r="R29" s="4" t="n">
         <v>1</v>
@@ -11015,7 +11058,7 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="P30" s="4" t="n">
@@ -11081,19 +11124,19 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Devarsh Surgical &amp; Maternity Hospital</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="P31" s="4" t="n">
-        <v>481</v>
+        <v>1497</v>
       </c>
       <c r="Q31" s="26" t="n">
-        <v>32.1</v>
+        <v>99.8</v>
       </c>
       <c r="R31" s="4" t="n">
         <v>1</v>
@@ -11262,7 +11305,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E3" s="15" t="n">
@@ -11299,7 +11342,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="P3" s="4" t="n">
@@ -11309,11 +11352,11 @@
         <v>23.1</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 29%) but map clicks don't convert (9%); rival Hospital / Psych hospital 8907 vs our 386 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 29%) but map clicks don't convert (9%); rival Hospital 8907 vs our 386 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11376,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
@@ -11404,7 +11447,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E5" s="15" t="n">
@@ -11441,7 +11484,7 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="P5" s="4" t="n">
@@ -11455,7 +11498,7 @@
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 36%) but map clicks don't convert (10%); rival Hospital / Psych hospital 11251 vs our 305 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 36%) but map clicks don't convert (10%); rival Hospital 11251 vs our 305 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11626,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="P7" s="4" t="n">
@@ -11597,7 +11640,7 @@
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 48%) but map clicks don't convert (9%); rival Hospital / Psych hospital 2542 vs our 260 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 48%) but map clicks don't convert (9%); rival Hospital 2542 vs our 260 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -11617,7 +11660,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E8" s="15" t="n">
@@ -11791,19 +11834,19 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Mauli Neurocare and Neurosurgery Hospital</t>
+          <t>Vertex Healing Centre</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Reiki therapist</t>
         </is>
       </c>
       <c r="P10" s="4" t="n">
-        <v>256</v>
+        <v>483</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>85.3</v>
+        <v>161</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>1</v>
@@ -11867,7 +11910,7 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Mental health service</t>
         </is>
       </c>
       <c r="P11" s="4" t="n">
@@ -11938,7 +11981,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Specialized hospital</t>
         </is>
       </c>
       <c r="P12" s="4" t="n">
@@ -12009,7 +12052,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
@@ -12019,7 +12062,7 @@
         <v>17.7</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
@@ -12080,7 +12123,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
@@ -12151,7 +12194,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
@@ -12217,19 +12260,19 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>1</v>
@@ -12288,19 +12331,19 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="Q17" s="26" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>1</v>
@@ -12364,7 +12407,7 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Psychologist</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
@@ -12485,19 +12528,19 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>Dr Krithishree S S</t>
+          <t>Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="P20" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="Q20" s="27" t="n">
-        <v>1.5</v>
+        <v>1244</v>
+      </c>
+      <c r="Q20" s="26" t="n">
+        <v>7.4</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1</v>
@@ -12556,22 +12599,22 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Dr Sagar Mundada</t>
+          <t>Growth Centre India Private Limited</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>788</v>
-      </c>
-      <c r="Q21" s="27" t="n">
-        <v>2</v>
+        <v>1833</v>
+      </c>
+      <c r="Q21" s="26" t="n">
+        <v>4.7</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
@@ -12627,19 +12670,19 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>Prerana Psychiatry &amp; Gynaecology Hospital</t>
+          <t>Spandana physiotherapy and sports clinic</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="P22" s="4" t="n">
-        <v>480</v>
+        <v>544</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R22" s="4" t="n">
         <v>0</v>
@@ -12769,19 +12812,19 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Dr. Hemant Sonanis - Best Psychiatrist and Counselor in Nashik</t>
+          <t>Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Ayurvedic clinic</t>
         </is>
       </c>
       <c r="P24" s="4" t="n">
-        <v>495</v>
+        <v>1382</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R24" s="4" t="n">
         <v>1</v>
@@ -12845,7 +12888,7 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>ENT Specialist</t>
         </is>
       </c>
       <c r="P25" s="4" t="n">
@@ -12982,19 +13025,19 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>Dr. Ravish Ranjan</t>
+          <t>Paramarsh Bharti</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="P27" s="4" t="n">
-        <v>586</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>1.5</v>
+        <v>994</v>
+      </c>
+      <c r="Q27" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -13053,19 +13096,19 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Dr. Mayank Agrawal</t>
+          <t>Best Career Counselling</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="P28" s="4" t="n">
-        <v>520</v>
+        <v>948</v>
       </c>
       <c r="Q28" s="26" t="n">
-        <v>15.8</v>
+        <v>28.7</v>
       </c>
       <c r="R28" s="4" t="n">
         <v>1</v>
@@ -13129,7 +13172,7 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="P29" s="4" t="n">
@@ -13266,19 +13309,19 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Dr G.SURESH KUMAR</t>
+          <t>Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Ayurvedic clinic</t>
         </is>
       </c>
       <c r="P31" s="4" t="n">
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="Q31" s="26" t="n">
-        <v>16.6</v>
+        <v>17.6</v>
       </c>
       <c r="R31" s="4" t="n">
         <v>1</v>
@@ -17575,37 +17618,37 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Redcliffe Labs - Ahmedabad | Full Body Checkup in Ahmedabad</t>
+          <t>GIPS Hospital and De-addiction Centre</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Psychiatrist</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>3455</v>
+        <v>15775</v>
       </c>
       <c r="G3" s="26" t="n">
-        <v>-3426</v>
+        <v>-15746</v>
       </c>
       <c r="H3" s="26" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J3" s="15" t="n">
         <v>2378</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (3455 vs 29)</t>
+          <t>BUILD REVIEWS — Psychiatrist rival far ahead (15775 vs 29)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +3426 to match)</t>
+          <t>Build reviews (need +15746 to match)</t>
         </is>
       </c>
     </row>
@@ -17630,7 +17673,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -17650,7 +17693,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Gynae / Fertility rival far ahead (413 vs 3)</t>
+          <t>BUILD REVIEWS — Fertility clinic rival far ahead (413 vs 3)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -17680,7 +17723,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Pathologist</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -17700,7 +17743,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (613 vs 53)</t>
+          <t>BUILD REVIEWS — Pathologist rival far ahead (613 vs 53)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -17725,35 +17768,35 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in HSR Layout</t>
+          <t>Redcliffe Labs: Diagnostic and Pathology Lab Bangalore | Full Body Checkup Bangalore (NABL Recognised)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1626</v>
+        <v>1932</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>-1288</v>
+        <v>-1594</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1626 vs 338)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1932 vs 338)</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1288 to match)</t>
+          <t>Build reviews (need +1594 to match)</t>
         </is>
       </c>
     </row>
@@ -17773,37 +17816,37 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in AECS Layout</t>
+          <t>Motherhood Fertility &amp; IVF Center - Best IVF Centre in Sarjapur, Bangalore | IUI, ICSI, Infertility Treatment</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>861</v>
+        <v>884</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>-852</v>
+        <v>-875</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.01</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>1237</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (861 vs 9)</t>
+          <t>BUILD REVIEWS — Fertility clinic rival far ahead (884 vs 9)</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +852 to match)</t>
+          <t>Build reviews (need +875 to match)</t>
         </is>
       </c>
     </row>
@@ -17823,37 +17866,37 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in HSR Layout</t>
+          <t>Redcliffe Labs: Diagnostic and Pathology Lab Bangalore | Full Body Checkup Bangalore (NABL Recognised)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1626</v>
+        <v>1932</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>-1288</v>
+        <v>-1594</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1447</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1626 vs 338)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1932 vs 338)</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1288 to match)</t>
+          <t>Build reviews (need +1594 to match)</t>
         </is>
       </c>
     </row>
@@ -17873,37 +17916,37 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in AECS Layout</t>
+          <t>Avance Derma</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Dermatologist</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>-473</v>
+        <v>-504</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>454</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (861 vs 388)</t>
+          <t>BUILD REVIEWS — Dermatologist rival far ahead (892 vs 388)</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +473 to match)</t>
+          <t>Build reviews (need +504 to match)</t>
         </is>
       </c>
     </row>
@@ -17923,22 +17966,22 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Cloudnine Hospital - Electronic City</t>
+          <t>Care Diagnostics</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4941</v>
+        <v>6449</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-4286</v>
+        <v>-5794</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0.3</v>
@@ -17948,12 +17991,12 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Gynae / Fertility rival far ahead (4941 vs 655)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (6449 vs 655)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +4286 to match)</t>
+          <t>Build reviews (need +5794 to match)</t>
         </is>
       </c>
     </row>
@@ -17973,37 +18016,37 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in HSR Layout</t>
+          <t>Orange Health Labs | Health Checkups &amp; Blood Tests at Home in Bangalore</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1626</v>
+        <v>18997</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>-1134</v>
+        <v>-18505</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>4582</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1626 vs 492)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 492)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1134 to match)</t>
+          <t>Build reviews (need +18505 to match)</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18071,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -18048,7 +18091,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (18997 vs 45)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 45)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -18073,37 +18116,37 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in Jayanagar</t>
+          <t>Orange Health Labs | Health Checkups &amp; Blood Tests at Home in Bangalore</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>833</v>
+        <v>18997</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>-495</v>
+        <v>-18659</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.41</v>
+        <v>0.02</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>4369</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (833 vs 338)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 338)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +495 to match)</t>
+          <t>Build reviews (need +18659 to match)</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18171,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -18148,7 +18191,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (5744 vs 385)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (5744 vs 385)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -18178,7 +18221,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -18198,7 +18241,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (842 vs 198)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (842 vs 198)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -18228,7 +18271,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -18248,7 +18291,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (18997 vs 338)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 338)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -18273,35 +18316,35 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Neuberg Anand Reference Laboratory - Rajajinagar offers Diagnostics, Lab Tests, Blood Tests, Health Checkup</t>
+          <t>Dr Lohit's Ayur Clinic</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1010</v>
+        <v>1396</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>-963</v>
+        <v>-1349</v>
       </c>
       <c r="H17" s="26" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1010 vs 47)</t>
+          <t>BUILD REVIEWS — Sexologist rival far ahead (1396 vs 47)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +963 to match)</t>
+          <t>Build reviews (need +1349 to match)</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18369,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
@@ -18346,7 +18389,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (21686 vs 627)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 627)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -18376,7 +18419,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -18396,7 +18439,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (21686 vs 47)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 47)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -18426,7 +18469,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -18446,7 +18489,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (21686 vs 47)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 47)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -18471,37 +18514,37 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Neuberg Anand Reference Laboratory - Vijayanagar offers Diagnostics, Lab Tests, Blood Tests, Health Checkup</t>
+          <t>Dr Lohit's Ayur Clinic</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1050</v>
+        <v>1396</v>
       </c>
       <c r="G21" s="26" t="n">
-        <v>-572</v>
+        <v>-918</v>
       </c>
       <c r="H21" s="26" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>2773</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1050 vs 478)</t>
+          <t>BUILD REVIEWS — Sexologist rival far ahead (1396 vs 478)</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +572 to match)</t>
+          <t>Build reviews (need +918 to match)</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18569,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
@@ -18546,7 +18589,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 861 vs 604</t>
+          <t>BUILD REVIEWS — Diagnostic center rival leads 861 vs 604</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -18571,35 +18614,35 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Neuberg Anand Reference Laboratory - Vidyaranyapuram offers Diagnostics, Lab Tests, Blood Tests, Health Checkup</t>
+          <t>Prima Diagnostics - Yelahanka</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1878</v>
+        <v>2395</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>-1878</v>
+        <v>-2395</v>
       </c>
       <c r="H23" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1878 vs 0)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (2395 vs 0)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1878 to match)</t>
+          <t>Build reviews (need +2395 to match)</t>
         </is>
       </c>
     </row>
@@ -18619,37 +18662,37 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs</t>
+          <t>Dr Diwakar's Clinic</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>641</v>
+        <v>1078</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>-625</v>
+        <v>-1062</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>1035</v>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (641 vs 16)</t>
+          <t>BUILD REVIEWS — Sexologist rival far ahead (1078 vs 16)</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +625 to match)</t>
+          <t>Build reviews (need +1062 to match)</t>
         </is>
       </c>
     </row>
@@ -18669,35 +18712,35 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Dr Shah's Clinic for Male Infertility &amp; Sexual Health</t>
+          <t>Hitech Labs | Ultrasound, Radiology &amp; Pathology Lab in Kilpauk</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Sexologist</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>791</v>
+        <v>6464</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>-471</v>
+        <v>-6144</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (791 vs 320)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (6464 vs 320)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +471 to match)</t>
+          <t>Build reviews (need +6144 to match)</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18765,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical laboratory</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
@@ -18742,7 +18785,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1238 vs 594)</t>
+          <t>BUILD REVIEWS — Medical laboratory rival far ahead (1238 vs 594)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -18772,7 +18815,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical laboratory</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -18792,7 +18835,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1238 vs 320)</t>
+          <t>BUILD REVIEWS — Medical laboratory rival far ahead (1238 vs 320)</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -18822,7 +18865,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
@@ -18842,7 +18885,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (851 vs 3)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (851 vs 3)</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -18867,37 +18910,37 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Hitech Labs | Ultrasound, Radiology &amp; Pathology Lab in T. Nagar</t>
+          <t>Scans World</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2294</v>
+        <v>4337</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>-1974</v>
+        <v>-4017</v>
       </c>
       <c r="H29" s="26" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J29" s="15" t="n">
         <v>5269</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (2294 vs 320)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (4337 vs 320)</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1974 to match)</t>
+          <t>Build reviews (need +4017 to match)</t>
         </is>
       </c>
     </row>
@@ -18917,37 +18960,37 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Hitech Labs | Ultrasound, Radiology &amp; Pathology Lab in Tambaram</t>
+          <t>Indian Scan</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2040</v>
+        <v>8968</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>-1892</v>
+        <v>-8820</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>1030</v>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (2040 vs 148)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (8968 vs 148)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1892 to match)</t>
+          <t>Build reviews (need +8820 to match)</t>
         </is>
       </c>
     </row>
@@ -18967,37 +19010,37 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Neuberg Diagnostics - Blood Tests, CT Scan, MRI, Health Checkups in OMR</t>
+          <t>Apollo Diagnostics |Blood Test Laboratory| Perumbakkam | NABL Accredited | Blood Sample Collection from Home</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="G31" s="26" t="n">
-        <v>-1111</v>
+        <v>-1146</v>
       </c>
       <c r="H31" s="26" t="n">
         <v>0.04</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J31" s="15" t="n">
         <v>2104</v>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1155 vs 44)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1190 vs 44)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1111 to match)</t>
+          <t>Build reviews (need +1146 to match)</t>
         </is>
       </c>
     </row>
@@ -19017,37 +19060,37 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Neuberg Diagnostics - Blood Tests, CT Scan, MRI, Health Checkups in OMR</t>
+          <t>AARTHI SCANS &amp; LABS | VELACHERY | DIAGNOSTIC CENTER</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1155</v>
+        <v>6775</v>
       </c>
       <c r="G32" s="26" t="n">
-        <v>-561</v>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>0.51</v>
+        <v>-6181</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>0.09</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>5652</v>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 1155 vs 594</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (6775 vs 594)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +561 to match)</t>
+          <t>Build reviews (need +6181 to match)</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19115,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Blood testing service</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
@@ -19092,7 +19135,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 413 vs 288</t>
+          <t>BUILD REVIEWS — Blood testing service rival leads 413 vs 288</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -19117,37 +19160,37 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Healthcare Ltd</t>
+          <t>GMERS Civil Hospital</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>General hospital</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>-147</v>
+        <v>567</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>-552</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>1674</v>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (162 vs 15)</t>
+          <t>BUILD REVIEWS — General hospital rival far ahead (567 vs 15)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +147 to match)</t>
+          <t>Build reviews (need +552 to match)</t>
         </is>
       </c>
     </row>
@@ -19167,37 +19210,37 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>JEEVANNAVAR SKIN CARE CLINIC</t>
+          <t>Dr Chetan K Ganteppanavar - Consultant Physician and Diabetologist - Kalpana Multispeciality Clinic Hubli, India</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>STD/HIV clinic</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>585</v>
+        <v>635</v>
       </c>
       <c r="G35" s="26" t="n">
-        <v>-554</v>
+        <v>-604</v>
       </c>
       <c r="H35" s="26" t="n">
         <v>0.05</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>593</v>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — STD/HIV clinic rival far ahead (585 vs 31)</t>
+          <t>BUILD REVIEWS — Doctor rival far ahead (635 vs 31)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +554 to match)</t>
+          <t>Build reviews (need +604 to match)</t>
         </is>
       </c>
     </row>
@@ -19217,37 +19260,37 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Panjagutta - Pathology &amp; Radiology Lab | Full Body Checkup</t>
+          <t>Vijaya Diagnostic Centre Ameerpet - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>7469</v>
+        <v>10590</v>
       </c>
       <c r="G36" s="26" t="n">
-        <v>-6522</v>
+        <v>-9643</v>
       </c>
       <c r="H36" s="26" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>3282</v>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (7469 vs 947)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (10590 vs 947)</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +6522 to match)</t>
+          <t>Build reviews (need +9643 to match)</t>
         </is>
       </c>
     </row>
@@ -19267,37 +19310,37 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Apex Diagnostics And Research Laboratory</t>
+          <t>Orange Health Labs | Health Checkups &amp; Blood Tests at Home in Hyderabad</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>543</v>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>404</v>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>1.74</v>
+        <v>4637</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>-3690</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>0.2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J37" s="15" t="n">
         <v>209</v>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (4637 vs 947)</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +3690 to match)</t>
         </is>
       </c>
     </row>
@@ -19365,35 +19408,35 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Redcliffe Labs - Hyderabad (NABL Recognised) | Diagnostic Centre Near Me | Blood Test</t>
+          <t>Vijaya Diagnostic Centre Alwal - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1642</v>
+        <v>6238</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>-1313</v>
+        <v>-5909</v>
       </c>
       <c r="H39" s="26" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1642 vs 329)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (6238 vs 329)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1313 to match)</t>
+          <t>Build reviews (need +5909 to match)</t>
         </is>
       </c>
     </row>
@@ -19413,37 +19456,37 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in Botanical Garden</t>
+          <t>Vijaya Diagnostic Centre Botanical Garden - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>545</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>-107</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>0.8</v>
+        <v>1894</v>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>-1456</v>
+      </c>
+      <c r="H40" s="26" t="n">
+        <v>0.23</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>3391</v>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 545 vs 438</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1894 vs 438)</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +107 to match)</t>
+          <t>Build reviews (need +1456 to match)</t>
         </is>
       </c>
     </row>
@@ -19463,37 +19506,37 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Mens Clinic</t>
+          <t>Vijaya Diagnostic Centre KPHB Phase-6 - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Sexologist</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>467</v>
+        <v>3827</v>
       </c>
       <c r="G41" s="26" t="n">
-        <v>-458</v>
+        <v>-3818</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J41" s="15" t="n">
         <v>1173</v>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (467 vs 9)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (3827 vs 9)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +458 to match)</t>
+          <t>Build reviews (need +3818 to match)</t>
         </is>
       </c>
     </row>
@@ -19513,37 +19556,37 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre BHEL -Ramachandrapuram - Pathology &amp; Radiology Lab | Full Body Checkup</t>
+          <t>Vijaya Diagnostic Centre Nallagandla - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4472</v>
+        <v>4992</v>
       </c>
       <c r="G42" s="26" t="n">
-        <v>-3482</v>
+        <v>-4002</v>
       </c>
       <c r="H42" s="26" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J42" s="15" t="n">
         <v>1280</v>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (4472 vs 990)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (4992 vs 990)</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +3482 to match)</t>
+          <t>Build reviews (need +4002 to match)</t>
         </is>
       </c>
     </row>
@@ -19563,37 +19606,37 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Orange Health Labs | Full Body Checkup &amp; Diagnostic Centre in Puppalaguda</t>
+          <t>Vijaya Diagnostic Centre Kokapet - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>754</v>
+        <v>2134</v>
       </c>
       <c r="G43" s="26" t="n">
-        <v>-567</v>
+        <v>-1947</v>
       </c>
       <c r="H43" s="26" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="15" t="n">
         <v>898</v>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (754 vs 187)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (2134 vs 187)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +567 to match)</t>
+          <t>Build reviews (need +1947 to match)</t>
         </is>
       </c>
     </row>
@@ -19613,37 +19656,37 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Sprint Diagnostics- Best MRI,CT,PET-CT-Scan &amp; Ultrasound at affordable price in AS Rao Nagar, Hyderabad</t>
+          <t>Vijaya Diagnostic Centre A.S. Rao Nagar - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1693</v>
+        <v>13163</v>
       </c>
       <c r="G44" s="26" t="n">
-        <v>-1364</v>
+        <v>-12834</v>
       </c>
       <c r="H44" s="26" t="n">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>2189</v>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1693 vs 329)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (13163 vs 329)</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1364 to match)</t>
+          <t>Build reviews (need +12834 to match)</t>
         </is>
       </c>
     </row>
@@ -19663,35 +19706,35 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>AARTHI SCANS &amp; LABS | KARKHANA | DIAGNOSTIC CENTER</t>
+          <t>Vijaya Diagnostic Centre S.D. Road - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2312</v>
+        <v>9056</v>
       </c>
       <c r="G45" s="26" t="n">
-        <v>-1983</v>
+        <v>-8727</v>
       </c>
       <c r="H45" s="26" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (2312 vs 329)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (9056 vs 329)</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1983 to match)</t>
+          <t>Build reviews (need +8727 to match)</t>
         </is>
       </c>
     </row>
@@ -19711,37 +19754,37 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>S.R. DIAGNOSTIC CENTRE BLOOD TEST FREE HOME SAMPLE COLLECTION SERVICE AVAILABLE</t>
+          <t>Vijaya Diagnostic Centre Boduppal - (Pheerzadiguda) - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>-61</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>0.54</v>
+        <v>7413</v>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>-7340</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0.01</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" s="15" t="n">
         <v>149</v>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 134 vs 73</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (7413 vs 73)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +61 to match)</t>
+          <t>Build reviews (need +7340 to match)</t>
         </is>
       </c>
     </row>
@@ -19761,37 +19804,37 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Vasanth Poly Clinic</t>
+          <t>Vijaya Diagnostic Centre Vanasthalipuram - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Sexologist</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1459</v>
+        <v>9270</v>
       </c>
       <c r="G47" s="26" t="n">
-        <v>-1386</v>
+        <v>-9197</v>
       </c>
       <c r="H47" s="26" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" s="15" t="n">
         <v>202</v>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (1459 vs 73)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (9270 vs 73)</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1386 to match)</t>
+          <t>Build reviews (need +9197 to match)</t>
         </is>
       </c>
     </row>
@@ -19811,35 +19854,35 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>-719</v>
+        <v>-1516</v>
       </c>
       <c r="H48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival far ahead (720 vs 1)</t>
+          <t>BUILD REVIEWS — Homeopath rival far ahead (1517 vs 1)</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +719 to match)</t>
+          <t>Build reviews (need +1516 to match)</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19907,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
@@ -19884,7 +19927,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1096 vs 90)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1096 vs 90)</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
@@ -19909,35 +19952,35 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Dr Nayan Gupta - Cancer Surgeon | Cancer Specialist | Surgical Oncologist | Tongue | Head &amp; Neck | Oral | Jaw | Indore</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>720</v>
+        <v>1517</v>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-719</v>
+        <v>-1516</v>
       </c>
       <c r="H50" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival far ahead (720 vs 1)</t>
+          <t>BUILD REVIEWS — Homeopath rival far ahead (1517 vs 1)</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +719 to match)</t>
+          <t>Build reviews (need +1516 to match)</t>
         </is>
       </c>
     </row>
@@ -19957,35 +20000,35 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Apollo 24|7 Lab Tests Near Me | Sree Rama Nagar | Home collection | Kurnool</t>
+          <t>Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G51" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>2</v>
+        <v>18578</v>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>-18566</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18578 vs 12)</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +18566 to match)</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20053,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Blood testing service</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
@@ -20028,7 +20071,7 @@
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1202 vs 380)</t>
+          <t>BUILD REVIEWS — Blood testing service rival far ahead (1202 vs 380)</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
@@ -20053,37 +20096,37 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>w centre for sexual wellness</t>
+          <t>Sparsha Diagnostics</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="G53" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="H53" s="28" t="n">
-        <v>1.51</v>
+        <v>785</v>
+      </c>
+      <c r="G53" s="26" t="n">
+        <v>-617</v>
+      </c>
+      <c r="H53" s="26" t="n">
+        <v>0.21</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J53" s="15" t="n">
         <v>743</v>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (785 vs 168)</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +617 to match)</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20151,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
@@ -20128,7 +20171,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 1066 vs 712</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival leads 1066 vs 712</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -20158,7 +20201,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
@@ -20178,7 +20221,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1228 vs 380)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (1228 vs 380)</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -20208,7 +20251,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
@@ -20226,7 +20269,7 @@
       <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (6925 vs 495)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (6925 vs 495)</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
@@ -20256,7 +20299,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
@@ -20276,7 +20319,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (15414 vs 382)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (15414 vs 382)</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -20306,7 +20349,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
@@ -20326,7 +20369,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (6925 vs 495)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (6925 vs 495)</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -20356,7 +20399,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
@@ -20376,7 +20419,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (5237 vs 391)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (5237 vs 391)</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
@@ -20406,7 +20449,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
@@ -20426,7 +20469,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (15414 vs 197)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (15414 vs 197)</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -20451,37 +20494,37 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Universe Diagnostics (Accredited by NABL, India)</t>
+          <t>Dr Lal PathLabs - Patient Service Centre</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>617</v>
+        <v>803</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>-67</v>
+        <v>-253</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J61" s="15" t="n">
         <v>2448</v>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 617 vs 550</t>
+          <t>BUILD REVIEWS — Diagnostic center rival leads 803 vs 550</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +67 to match)</t>
+          <t>Build reviews (need +253 to match)</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20549,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Blood testing service</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
@@ -20526,7 +20569,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (506 vs 4)</t>
+          <t>BUILD REVIEWS — Blood testing service rival far ahead (506 vs 4)</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -20551,37 +20594,37 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Agilus Diagnostics Dr. Phadke Labs - Mulund East, Mumbai</t>
+          <t>Dr. Maratha Clinic | Sexual Health Expert in Ayurveda</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>372</v>
+        <v>488</v>
       </c>
       <c r="G63" s="26" t="n">
-        <v>-362</v>
+        <v>-478</v>
       </c>
       <c r="H63" s="26" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J63" s="15" t="n">
         <v>105</v>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (372 vs 10)</t>
+          <t>BUILD REVIEWS — Sexologist rival far ahead (488 vs 10)</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +362 to match)</t>
+          <t>Build reviews (need +478 to match)</t>
         </is>
       </c>
     </row>
@@ -20606,7 +20649,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
@@ -20626,7 +20669,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 563 vs 515</t>
+          <t>BUILD REVIEWS — Diagnostic center rival leads 563 vs 515</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -20656,7 +20699,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
@@ -20676,7 +20719,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (318 vs 0)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (318 vs 0)</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -20701,37 +20744,37 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Santasa Fertility &amp; IVF, Mysore</t>
+          <t>Apollo Clinic</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="G66" s="28" t="n">
-        <v>349</v>
-      </c>
-      <c r="H66" s="28" t="n">
-        <v>2.74</v>
+        <v>4866</v>
+      </c>
+      <c r="G66" s="26" t="n">
+        <v>-4316</v>
+      </c>
+      <c r="H66" s="26" t="n">
+        <v>0.11</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>1404</v>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (4866 vs 550)</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +4316 to match)</t>
         </is>
       </c>
     </row>
@@ -20751,37 +20794,37 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs</t>
+          <t>Krisham Men's Health (Sexology) And Diabetis Clinic</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Sexologist</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1036</v>
+        <v>1566</v>
       </c>
       <c r="G67" s="26" t="n">
-        <v>-857</v>
+        <v>-1387</v>
       </c>
       <c r="H67" s="26" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J67" s="15" t="n">
         <v>531</v>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1036 vs 179)</t>
+          <t>BUILD REVIEWS — Sexologist rival far ahead (1566 vs 179)</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +857 to match)</t>
+          <t>Build reviews (need +1387 to match)</t>
         </is>
       </c>
     </row>
@@ -20801,37 +20844,37 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Kamatwade</t>
+          <t>Unique Multicare Clinic</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="G68" s="27" t="n">
-        <v>-92</v>
-      </c>
-      <c r="H68" s="27" t="n">
-        <v>0.52</v>
+        <v>4937</v>
+      </c>
+      <c r="G68" s="26" t="n">
+        <v>-4838</v>
+      </c>
+      <c r="H68" s="26" t="n">
+        <v>0.02</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J68" s="15" t="n">
         <v>1547</v>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 191 vs 99</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (4937 vs 99)</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +92 to match)</t>
+          <t>Build reviews (need +4838 to match)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20899,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical diagnostic imaging center</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
@@ -20876,7 +20919,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1045 vs 260)</t>
+          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (1045 vs 260)</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -20901,37 +20944,37 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Shelar Hospital</t>
+          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Old Panvel</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>410</v>
+        <v>691</v>
       </c>
       <c r="G70" s="26" t="n">
-        <v>-344</v>
+        <v>-625</v>
       </c>
       <c r="H70" s="26" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>1368</v>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Clinic rival far ahead (410 vs 66)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (691 vs 66)</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +344 to match)</t>
+          <t>Build reviews (need +625 to match)</t>
         </is>
       </c>
     </row>
@@ -20956,7 +20999,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>STD testing service</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
@@ -20976,7 +21019,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1202 vs 380)</t>
+          <t>BUILD REVIEWS — STD testing service rival far ahead (1202 vs 380)</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -21001,37 +21044,37 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>healthcare nt sickcare | Pathology Lab in Pune</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>393</v>
+        <v>704</v>
       </c>
       <c r="G72" s="26" t="n">
-        <v>-312</v>
+        <v>-623</v>
       </c>
       <c r="H72" s="26" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J72" s="15" t="n">
         <v>1053</v>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (393 vs 81)</t>
+          <t>BUILD REVIEWS — Homeopath rival far ahead (704 vs 81)</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +312 to match)</t>
+          <t>Build reviews (need +623 to match)</t>
         </is>
       </c>
     </row>
@@ -21051,37 +21094,37 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Dr Tayades Pathlab Diagnostic Center</t>
+          <t>Metropolis Labs - Diagnostic Centre &amp; Blood Test in Nigadi, Pune</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>449</v>
-      </c>
-      <c r="G73" s="27" t="n">
-        <v>-259</v>
+        <v>725</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <v>-535</v>
       </c>
       <c r="H73" s="26" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J73" s="15" t="n">
         <v>697</v>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (449 vs 190)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (725 vs 190)</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +259 to match)</t>
+          <t>Build reviews (need +535 to match)</t>
         </is>
       </c>
     </row>
@@ -21101,22 +21144,22 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Homeo Care Clinic - Dr. Vaseem Choudhary | Homeopathic Clinic</t>
+          <t>Vijaya PH Diagnostic Centre</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>591</v>
-      </c>
-      <c r="G74" s="27" t="n">
-        <v>-142</v>
-      </c>
-      <c r="H74" s="27" t="n">
-        <v>0.76</v>
+        <v>11472</v>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>-11023</v>
+      </c>
+      <c r="H74" s="26" t="n">
+        <v>0.04</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>0.5</v>
@@ -21126,12 +21169,12 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Clinic rival leads 591 vs 449</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (11472 vs 449)</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +142 to match)</t>
+          <t>Build reviews (need +11023 to match)</t>
         </is>
       </c>
     </row>
@@ -21156,7 +21199,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
@@ -21176,7 +21219,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1000 vs 130)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1000 vs 130)</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -21206,7 +21249,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
@@ -21226,7 +21269,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (2991 vs 330)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (2991 vs 330)</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -21251,37 +21294,37 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Krsnaa Diagnostics | Blood Test &amp; Diagnostic Centre In Pune</t>
+          <t>Sunrise Diagnostics, Sonography, Xray, CT Scan, Blood test in kothurd Pune</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1860</v>
+        <v>3234</v>
       </c>
       <c r="G77" s="26" t="n">
-        <v>-1504</v>
+        <v>-2878</v>
       </c>
       <c r="H77" s="26" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J77" s="15" t="n">
         <v>1242</v>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (1860 vs 356)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (3234 vs 356)</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1504 to match)</t>
+          <t>Build reviews (need +2878 to match)</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21349,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Medical laboratory</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -21326,7 +21369,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (4987 vs 305)</t>
+          <t>BUILD REVIEWS — Medical laboratory rival far ahead (4987 vs 305)</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -21356,7 +21399,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
@@ -21376,7 +21419,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (640 vs 2)</t>
+          <t>BUILD REVIEWS — Diagnostic center rival far ahead (640 vs 2)</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -21401,35 +21444,35 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Metropolis Labs | Blood Test &amp; Diagnostic Centre in Rajkot</t>
+          <t>Dr. Bhatt Pathology Laboratory - Main Branch</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>633</v>
+        <v>5653</v>
       </c>
       <c r="G80" s="26" t="n">
-        <v>-633</v>
+        <v>-5653</v>
       </c>
       <c r="H80" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (633 vs 0)</t>
+          <t>BUILD REVIEWS — Laboratory rival far ahead (5653 vs 0)</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +633 to match)</t>
+          <t>Build reviews (need +5653 to match)</t>
         </is>
       </c>
     </row>
@@ -21449,37 +21492,37 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Krsnaa Diagnostics | Blood Test &amp; Diagnostic Centre In Ranchi</t>
+          <t>Health Home</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Diagnostic center</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>404</v>
-      </c>
-      <c r="G81" s="27" t="n">
-        <v>-12</v>
+        <v>761</v>
+      </c>
+      <c r="G81" s="26" t="n">
+        <v>-369</v>
       </c>
       <c r="H81" s="27" t="n">
-        <v>0.97</v>
+        <v>0.52</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J81" s="15" t="n">
         <v>728</v>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival leads 404 vs 392</t>
+          <t>BUILD REVIEWS — Diagnostic center rival leads 761 vs 392</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +12 to match)</t>
+          <t>Build reviews (need +369 to match)</t>
         </is>
       </c>
     </row>
@@ -21499,37 +21542,37 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Naveli Hospital | Dr Keyur Yagnik | Dr Reshma Yagnik | Bariatric Surgeon | Hernia Surgeon</t>
+          <t>IID Hospital - Institute of Infectious Diseases</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>HIV testing center</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>870</v>
+        <v>1162</v>
       </c>
       <c r="G82" s="26" t="n">
-        <v>-837</v>
+        <v>-1129</v>
       </c>
       <c r="H82" s="26" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>3372</v>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Clinic rival far ahead (870 vs 33)</t>
+          <t>BUILD REVIEWS — HIV testing center rival far ahead (1162 vs 33)</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +837 to match)</t>
+          <t>Build reviews (need +1129 to match)</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21597,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Gynae / Fertility</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
@@ -21572,7 +21615,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Gynae / Fertility rival far ahead (156 vs 0)</t>
+          <t>BUILD REVIEWS — Fertility clinic rival far ahead (156 vs 0)</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -21597,37 +21640,37 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Devarsh Surgical &amp; Maternity Hospital</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Clinic</t>
+          <t>Homeopath</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>481</v>
+        <v>1497</v>
       </c>
       <c r="G84" s="26" t="n">
-        <v>-466</v>
+        <v>-1482</v>
       </c>
       <c r="H84" s="26" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>332</v>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Clinic rival far ahead (481 vs 15)</t>
+          <t>BUILD REVIEWS — Homeopath rival far ahead (1497 vs 15)</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +466 to match)</t>
+          <t>Build reviews (need +1482 to match)</t>
         </is>
       </c>
     </row>
@@ -21647,37 +21690,37 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Home Collection Lab (BLOOD TESTING SERVICE)</t>
+          <t>Dr.MEGHANATH YENNI MD;DNB</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Diagnostic lab</t>
+          <t>Specialized clinic</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="G85" s="27" t="n">
-        <v>-184</v>
+        <v>567</v>
+      </c>
+      <c r="G85" s="26" t="n">
+        <v>-526</v>
       </c>
       <c r="H85" s="26" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J85" s="15" t="n">
         <v>476</v>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic lab rival far ahead (225 vs 41)</t>
+          <t>BUILD REVIEWS — Specialized clinic rival far ahead (567 vs 41)</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +184 to match)</t>
+          <t>Build reviews (need +526 to match)</t>
         </is>
       </c>
     </row>
@@ -21847,37 +21890,37 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Mauli Neurocare and Neurosurgery Hospital</t>
+          <t>Vertex Healing Centre</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Reiki therapist</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>-253</v>
+        <v>483</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>-480</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.01</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="15" t="n">
         <v>164</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (256 vs 3)</t>
+          <t>BUILD REVIEWS — Reiki therapist rival far ahead (483 vs 3)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +253 to match)</t>
+          <t>Build reviews (need +480 to match)</t>
         </is>
       </c>
     </row>
@@ -21902,7 +21945,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Mental health service</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -21922,7 +21965,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Therapist / Counsellor rival far ahead (1237 vs 53)</t>
+          <t>BUILD REVIEWS — Mental health service rival far ahead (1237 vs 53)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -21995,37 +22038,37 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Dr Santhosh Gastro and Liver centre</t>
+          <t>Healing Hub</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Mental health service</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>-182</v>
+        <v>310</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>-301</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>1237</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (191 vs 9)</t>
+          <t>BUILD REVIEWS — Mental health service rival far ahead (310 vs 9)</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +182 to match)</t>
+          <t>Build reviews (need +301 to match)</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22143,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Specialized clinic</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -22120,7 +22163,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (3323 vs 9)</t>
+          <t>BUILD REVIEWS — Specialized clinic rival far ahead (3323 vs 9)</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -22150,7 +22193,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -22170,7 +22213,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (7860 vs 655)</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (7860 vs 655)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -22195,37 +22238,37 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>YourDOST</t>
+          <t>Padithem Health Care</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>549</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>-161</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>0.71</v>
+        <v>1563</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>-1175</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>0.25</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>4582</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Therapist / Counsellor rival leads 549 vs 388</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (1563 vs 388)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +161 to match)</t>
+          <t>Build reviews (need +1175 to match)</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22293,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -22270,7 +22313,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival leads 757 vs 746</t>
+          <t>BUILD REVIEWS — Medical clinic rival leads 757 vs 746</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -22300,7 +22343,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -22320,7 +22363,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (2209 vs 492)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (2209 vs 492)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -22350,7 +22393,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -22370,7 +22413,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (3077 vs 385)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (3077 vs 385)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -22395,37 +22438,37 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>BrahVishMah</t>
+          <t>Academics and Beyond | Career Counseling | Soft Skills | Personality Development</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>411</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-213</v>
+        <v>577</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-379</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>678</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Therapist / Counsellor rival far ahead (411 vs 198)</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (577 vs 198)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +213 to match)</t>
+          <t>Build reviews (need +379 to match)</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22691,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -22668,7 +22711,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (8907 vs 47)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (8907 vs 47)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -22693,37 +22736,37 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vikram Arunachalam</t>
+          <t>UNIQUE TRUTH</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>351</v>
-      </c>
-      <c r="G21" s="28" t="n">
-        <v>127</v>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>1.36</v>
+        <v>647</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>-169</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0.74</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>2773</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Counselor rival leads 647 vs 478</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +169 to match)</t>
         </is>
       </c>
     </row>
@@ -22748,7 +22791,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
@@ -22768,7 +22811,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival leads 719 vs 604</t>
+          <t>BUILD REVIEWS — Hospital rival leads 719 vs 604</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -22798,7 +22841,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
@@ -22816,7 +22859,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (685 vs 0)</t>
+          <t>BUILD REVIEWS — Doctor rival far ahead (685 vs 0)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -22846,7 +22889,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Specialized hospital</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
@@ -22866,7 +22909,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (1451 vs 16)</t>
+          <t>BUILD REVIEWS — Specialized hospital rival far ahead (1451 vs 16)</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -22939,37 +22982,37 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>The Optimind Clinic- Dr. Sathish Kumar | Psychiatrist | Chennai</t>
+          <t>Chennai Counseling Services &amp; CCS Academy</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Family counselor</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>414</v>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>3.3</v>
+        <v>1137</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>-543</v>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>0.52</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>239</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Family counselor rival leads 1137 vs 594</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +543 to match)</t>
         </is>
       </c>
     </row>
@@ -22989,37 +23032,37 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>AGAM Anxiety Wellness Clinic</t>
+          <t>Emocare (Counseling,Life Coaching and Training)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>584</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>-264</v>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>0.55</v>
+        <v>4455</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>-4135</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>718</v>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival leads 584 vs 320</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (4455 vs 320)</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +264 to match)</t>
+          <t>Build reviews (need +4135 to match)</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23237,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Mental health service</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -23214,7 +23257,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Therapist / Counsellor rival far ahead (373 vs 44)</t>
+          <t>BUILD REVIEWS — Mental health service rival far ahead (373 vs 44)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -23244,7 +23287,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -23264,7 +23307,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (5650 vs 594)</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (5650 vs 594)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -23344,7 +23387,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
@@ -23364,7 +23407,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (15626 vs 15)</t>
+          <t>BUILD REVIEWS — Doctor rival far ahead (15626 vs 15)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -23592,7 +23635,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
@@ -23610,7 +23653,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (4315 vs 329)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (4315 vs 329)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -23690,7 +23733,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
@@ -23710,7 +23753,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (3431 vs 9)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (3431 vs 9)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -23740,7 +23783,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
@@ -23760,7 +23803,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (11820 vs 990)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (11820 vs 990)</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -23790,7 +23833,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
@@ -23810,7 +23853,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (1027 vs 187)</t>
+          <t>BUILD REVIEWS — Doctor rival far ahead (1027 vs 187)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -23840,7 +23883,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
@@ -23860,7 +23903,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (4118 vs 329)</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (4118 vs 329)</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -23890,7 +23933,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
@@ -23908,7 +23951,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (5776 vs 329)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (5776 vs 329)</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
@@ -23938,7 +23981,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
@@ -23958,7 +24001,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (8581 vs 73)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (8581 vs 73)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -24033,35 +24076,35 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>-351</v>
+        <v>-528</v>
       </c>
       <c r="H48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (352 vs 1)</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (529 vs 1)</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +351 to match)</t>
+          <t>Build reviews (need +528 to match)</t>
         </is>
       </c>
     </row>
@@ -24131,35 +24174,35 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Dr Vijay Niranjan Neuropsychiatry Clinic | Best Psychiatrist Indore</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>352</v>
+        <v>529</v>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-351</v>
+        <v>-528</v>
       </c>
       <c r="H50" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (352 vs 1)</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (529 vs 1)</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +351 to match)</t>
+          <t>Build reviews (need +528 to match)</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24227,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Psychologist</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
@@ -24202,7 +24245,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Therapist / Counsellor rival far ahead (572 vs 12)</t>
+          <t>BUILD REVIEWS — Psychologist rival far ahead (572 vs 12)</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
@@ -24275,37 +24318,37 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Dr Krithishree S S</t>
+          <t>Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Fertility clinic</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>-86</v>
-      </c>
-      <c r="H53" s="27" t="n">
-        <v>0.66</v>
+        <v>1244</v>
+      </c>
+      <c r="G53" s="26" t="n">
+        <v>-1076</v>
+      </c>
+      <c r="H53" s="26" t="n">
+        <v>0.14</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J53" s="15" t="n">
         <v>743</v>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival leads 254 vs 168</t>
+          <t>BUILD REVIEWS — Fertility clinic rival far ahead (1244 vs 168)</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +86 to match)</t>
+          <t>Build reviews (need +1076 to match)</t>
         </is>
       </c>
     </row>
@@ -24375,37 +24418,37 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Manarogya Psychiatry Clinic Dr.Pratik Surandashe Dr. Mansi Jain</t>
+          <t>Brainwonders</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>327</v>
-      </c>
-      <c r="G55" s="28" t="n">
-        <v>53</v>
-      </c>
-      <c r="H55" s="28" t="n">
-        <v>1.16</v>
+        <v>996</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>-616</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0.38</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" s="15" t="n">
         <v>1072</v>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (996 vs 380)</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +616 to match)</t>
         </is>
       </c>
     </row>
@@ -24425,35 +24468,35 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Dr. Aslam Khan Clinic</t>
+          <t>Aara Education Consultancy - Study Abroad and Career Counsellor in Mumbai</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>494</v>
-      </c>
-      <c r="G56" s="28" t="n">
+        <v>509</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I56" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="H56" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>2.6</v>
       </c>
       <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Counselor rival leads 509 vs 495</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +14 to match)</t>
         </is>
       </c>
     </row>
@@ -24473,37 +24516,37 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Manpravah</t>
+          <t>Astitva Clinic</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Therapist / Counsellor</t>
+          <t>Psychologist</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>284</v>
-      </c>
-      <c r="G57" s="28" t="n">
-        <v>98</v>
-      </c>
-      <c r="H57" s="28" t="n">
-        <v>1.35</v>
+        <v>774</v>
+      </c>
+      <c r="G57" s="26" t="n">
+        <v>-392</v>
+      </c>
+      <c r="H57" s="26" t="n">
+        <v>0.49</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J57" s="15" t="n">
         <v>1918</v>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Psychologist rival far ahead (774 vs 382)</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +392 to match)</t>
         </is>
       </c>
     </row>
@@ -24578,7 +24621,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Psychiatric hospital</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
@@ -24598,7 +24641,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival leads 649 vs 391</t>
+          <t>BUILD REVIEWS — Psychiatric hospital rival leads 649 vs 391</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
@@ -24673,25 +24716,25 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Dr Sagar Mundada</t>
+          <t>Holistic Mind Therapy</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="G61" s="28" t="n">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J61" s="15" t="n">
         <v>2448</v>
@@ -24728,7 +24771,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>General hospital</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
@@ -24748,7 +24791,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (628 vs 4)</t>
+          <t>BUILD REVIEWS — General hospital rival far ahead (628 vs 4)</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -24773,37 +24816,37 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>IPH Thane - Tridal, Avahan, Elegance, Aakalan, Maitra, Shikshak Mitra, Mission Excellence, Manovikas, Jidnyasa, Sage</t>
+          <t>Mending Mind - Psychologist | Mental Health services</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>-230</v>
+        <v>-244</v>
       </c>
       <c r="H63" s="26" t="n">
         <v>0.04</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J63" s="15" t="n">
         <v>105</v>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (240 vs 10)</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (254 vs 10)</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +230 to match)</t>
+          <t>Build reviews (need +244 to match)</t>
         </is>
       </c>
     </row>
@@ -24823,37 +24866,37 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Dr. Pradeep Tripathi - Best Laser &amp; Laparoscopic Surgeon, Appendix, Hernia, Gallbladder Stone, Bariatric Surgeon in Thane</t>
+          <t>Depth - Counselling, Special Education &amp; Remedial Centre in Thane</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>517</v>
-      </c>
-      <c r="G64" s="27" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H64" s="27" t="n">
-        <v>1</v>
+        <v>279</v>
+      </c>
+      <c r="G64" s="28" t="n">
+        <v>236</v>
+      </c>
+      <c r="H64" s="28" t="n">
+        <v>1.85</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>2146</v>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival leads 517 vs 515</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +2 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24921,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
@@ -24898,7 +24941,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (641 vs 0)</t>
+          <t>BUILD REVIEWS — Doctor rival far ahead (641 vs 0)</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -24923,25 +24966,25 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Prerana Psychiatry &amp; Gynaecology Hospital</t>
+          <t>Spandana physiotherapy and sports clinic</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>480</v>
+        <v>544</v>
       </c>
       <c r="G66" s="28" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>1404</v>
@@ -25023,37 +25066,37 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Dr. Hemant Sonanis - Best Psychiatrist and Counselor in Nashik</t>
+          <t>Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Ayurvedic clinic</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>495</v>
+        <v>1382</v>
       </c>
       <c r="G68" s="26" t="n">
-        <v>-396</v>
+        <v>-1283</v>
       </c>
       <c r="H68" s="26" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J68" s="15" t="n">
         <v>1547</v>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (495 vs 99)</t>
+          <t>BUILD REVIEWS — Ayurvedic clinic rival far ahead (1382 vs 99)</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +396 to match)</t>
+          <t>Build reviews (need +1283 to match)</t>
         </is>
       </c>
     </row>
@@ -25073,37 +25116,37 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Polaris Hospital</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psychologist</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2387</v>
+        <v>694</v>
       </c>
       <c r="G69" s="26" t="n">
-        <v>-2127</v>
+        <v>-434</v>
       </c>
       <c r="H69" s="26" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J69" s="15" t="n">
         <v>845</v>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival far ahead (2387 vs 260)</t>
+          <t>BUILD REVIEWS — Psychologist rival far ahead (694 vs 260)</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +2127 to match)</t>
+          <t>Build reviews (need +434 to match)</t>
         </is>
       </c>
     </row>
@@ -25128,7 +25171,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
@@ -25148,7 +25191,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (2542 vs 66)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (2542 vs 66)</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
@@ -25228,7 +25271,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Mental Hospital</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
@@ -25248,7 +25291,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (436 vs 81)</t>
+          <t>BUILD REVIEWS — Mental Hospital rival far ahead (436 vs 81)</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -25278,7 +25321,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
@@ -25328,7 +25371,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
@@ -25348,7 +25391,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (11251 vs 449)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (11251 vs 449)</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -25378,7 +25421,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Hospital / Psych hospital</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
@@ -25398,7 +25441,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital / Psych hospital rival far ahead (755 vs 130)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (755 vs 130)</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -25428,7 +25471,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Clinic / Doctor</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
@@ -25448,7 +25491,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Clinic / Doctor rival far ahead (2434 vs 330)</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (2434 vs 330)</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -25473,37 +25516,37 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Dr Swapnil Deshmukh MBBS,MD</t>
+          <t>Neha Yeole Psychotherapist Counsellor Therapist Pune</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>-142</v>
+        <v>-175</v>
       </c>
       <c r="H77" s="27" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J77" s="15" t="n">
         <v>1242</v>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival leads 498 vs 356</t>
+          <t>BUILD REVIEWS — Counselor rival leads 531 vs 356</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +142 to match)</t>
+          <t>Build reviews (need +175 to match)</t>
         </is>
       </c>
     </row>
@@ -25523,37 +25566,37 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Dr. Neha Gupta (Giri) Cognivia Psychiatry| Psychiatrist in PCMC and Pune</t>
+          <t>Toshniwal Clinic | Family Physician | Physiotherapy | Nutrition</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Medical clinic</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="G78" s="26" t="n">
-        <v>-321</v>
+        <v>-648</v>
       </c>
       <c r="H78" s="26" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>1432</v>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (626 vs 305)</t>
+          <t>BUILD REVIEWS — Medical clinic rival far ahead (953 vs 305)</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +321 to match)</t>
+          <t>Build reviews (need +648 to match)</t>
         </is>
       </c>
     </row>
@@ -25573,37 +25616,37 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Dr. Bakhru's</t>
+          <t>Dr.Akash Nema (Raman Clinic)</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psychiatrist</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2214</v>
+        <v>558</v>
       </c>
       <c r="G79" s="26" t="n">
-        <v>-2212</v>
+        <v>-556</v>
       </c>
       <c r="H79" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" s="15" t="n">
         <v>190</v>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival far ahead (2214 vs 2)</t>
+          <t>BUILD REVIEWS — Psychiatrist rival far ahead (558 vs 2)</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +2212 to match)</t>
+          <t>Build reviews (need +556 to match)</t>
         </is>
       </c>
     </row>
@@ -25671,37 +25714,37 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Dr. Ravish Ranjan</t>
+          <t>Paramarsh Bharti</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>586</v>
-      </c>
-      <c r="G81" s="27" t="n">
-        <v>-194</v>
-      </c>
-      <c r="H81" s="27" t="n">
-        <v>0.67</v>
+        <v>994</v>
+      </c>
+      <c r="G81" s="26" t="n">
+        <v>-602</v>
+      </c>
+      <c r="H81" s="26" t="n">
+        <v>0.39</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J81" s="15" t="n">
         <v>728</v>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival leads 586 vs 392</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (994 vs 392)</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +194 to match)</t>
+          <t>Build reviews (need +602 to match)</t>
         </is>
       </c>
     </row>
@@ -25721,37 +25764,37 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Dr. Mayank Agrawal</t>
+          <t>Best Career Counselling</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Counselor</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>520</v>
+        <v>948</v>
       </c>
       <c r="G82" s="26" t="n">
-        <v>-487</v>
+        <v>-915</v>
       </c>
       <c r="H82" s="26" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>3372</v>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (520 vs 33)</t>
+          <t>BUILD REVIEWS — Counselor rival far ahead (948 vs 33)</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +487 to match)</t>
+          <t>Build reviews (need +915 to match)</t>
         </is>
       </c>
     </row>
@@ -25771,35 +25814,35 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Siddaganga Medical College &amp; Research Institute</t>
+          <t>GANGA HOSPITAL Tumkur</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1139</v>
+        <v>453</v>
       </c>
       <c r="G83" s="26" t="n">
-        <v>-1139</v>
+        <v>-453</v>
       </c>
       <c r="H83" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Other rival far ahead (1139 vs 0)</t>
+          <t>BUILD REVIEWS — Hospital rival far ahead (453 vs 0)</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1139 to match)</t>
+          <t>Build reviews (need +453 to match)</t>
         </is>
       </c>
     </row>
@@ -25869,37 +25912,37 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Dr G.SURESH KUMAR</t>
+          <t>Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Psychiatrist</t>
+          <t>Ayurvedic clinic</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="G85" s="26" t="n">
-        <v>-639</v>
+        <v>-679</v>
       </c>
       <c r="H85" s="26" t="n">
         <v>0.06</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J85" s="15" t="n">
         <v>476</v>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (680 vs 41)</t>
+          <t>BUILD REVIEWS — Ayurvedic clinic rival far ahead (720 vs 41)</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +639 to match)</t>
+          <t>Build reviews (need +679 to match)</t>
         </is>
       </c>
     </row>

--- a/Competition_Action_Plan.xlsx
+++ b/Competition_Action_Plan.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Shubham Hi-Tech Hospital and Test Tube Baby Centre 413 vs our median 3).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1517 vs our median 1).</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3131,11 +3131,11 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Shubham Hi-Tech Hospital and Test Tube Baby Centre (413)</t>
+          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1517)</t>
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1517 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup 18578 vs our median 12).</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3217,11 +3217,11 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1517)</t>
+          <t>Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup (18578)</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup 18578 vs our median 12).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Unique Diagnostic Centre 1202 vs our median 380).</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -3260,11 +3260,11 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Kurnool (Gayathri Estate) - Pathology &amp; Radiology Lab | Full Body Checkup (18578)</t>
+          <t>Unique Diagnostic Centre (1202)</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>12</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Unique Diagnostic Centre 1202 vs our median 380).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bhatt Pathology Laboratory - Main Branch 5653 vs our median 0).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3303,11 +3303,11 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Unique Diagnostic Centre (1202)</t>
+          <t>Dr. Bhatt Pathology Laboratory - Main Branch (5653)</t>
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Tumkur</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pathkind Labs 640 vs our median 2).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Indira IVF Fertility Centre in Tumkur - Best IVF Centre 156 vs our median 0).</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -3346,22 +3346,22 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Pathkind Labs (640)</t>
+          <t>Indira IVF Fertility Centre in Tumkur - Best IVF Centre (156)</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bhatt Pathology Laboratory - Main Branch 5653 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival GIPS Hospital and De-addiction Centre 15776 vs our median 29).</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3389,22 +3389,22 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Dr. Bhatt Pathology Laboratory - Main Branch (5653)</t>
+          <t>GIPS Hospital and De-addiction Centre (15776)</t>
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Amravati</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Health Home 761 vs our median 392).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vertex Healing Centre 483 vs our median 3).</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -3432,22 +3432,22 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Health Home (761)</t>
+          <t>Vertex Healing Centre (483)</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>392</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Tumkur</t>
+          <t>Aurangabad</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Indira IVF Fertility Centre in Tumkur - Best IVF Centre 156 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad 1237 vs our median 53).</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Indira IVF Fertility Centre in Tumkur - Best IVF Centre (156)</t>
+          <t>Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad (1237)</t>
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Mental Health</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr Batra’s Homeopathy, Hair &amp; Skin Clinic 1497 vs our median 15).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार 1451 vs our median 16).</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -3518,11 +3518,11 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Dr Batra’s Homeopathy, Hair &amp; Skin Clinic (1497)</t>
+          <t>Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार (1451)</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival GIPS Hospital and De-addiction Centre 15776 vs our median 29).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival SMVS Swaminarayan Hospital 15626 vs our median 15).</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3561,11 +3561,11 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>GIPS Hospital and De-addiction Centre (15776)</t>
+          <t>SMVS Swaminarayan Hospital (15626)</t>
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Amravati</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Vertex Healing Centre 483 vs our median 3).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3604,11 +3604,11 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Vertex Healing Centre (483)</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Aurangabad</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad 1237 vs our median 53).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Pranit Psychological Counseling &amp; Testing Center - IQ testing Aptitude &amp; career counseling in Aurangabad (1237)</t>
+          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार 1451 vs our median 16).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival YASH Relationship Centre (Lenin Perumalla Psychologist) 572 vs our median 12).</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Prayas Nasha Mukti evam Manochikitsa Kendra (Psychiatric Hospital &amp; Rehabilitation center)आयुष्मान योजना से निःशुल्क उपचार (1451)</t>
+          <t>YASH Relationship Centre (Lenin Perumalla Psychologist) (572)</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival SMVS Swaminarayan Hospital 15626 vs our median 15).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai 624 vs our median 380).</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -3733,11 +3733,11 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>SMVS Swaminarayan Hospital (15626)</t>
+          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai (624)</t>
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka 1244 vs our median 168).</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
@@ -3776,11 +3776,11 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
+          <t>Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka (1244)</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling 529 vs our median 1).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Sourabh Pal 592 vs our median 179).</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -3819,11 +3819,11 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Fly Future Education | Best Overseas Education Consultant in Indore | MBBS in Abroad &amp; India | NEET Counselling (529)</t>
+          <t>Dr. Sourabh Pal (592)</t>
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival YASH Relationship Centre (Lenin Perumalla Psychologist) 572 vs our median 12).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik 1382 vs our median 99).</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>YASH Relationship Centre (Lenin Perumalla Psychologist) (572)</t>
+          <t>Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik (1382)</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai 624 vs our median 380).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bakhru's 2214 vs our median 2).</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -3905,11 +3905,11 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai (624)</t>
+          <t>Dr. Bakhru's (2214)</t>
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>380</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka 1244 vs our median 168).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot 1479 vs our median 0).</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3948,11 +3948,11 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Birla Fertility &amp; IVF - Best IVF Centre in Mangalore, Karnataka (1244)</t>
+          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Sourabh Pal 592 vs our median 179).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Paramarsh Bharti 994 vs our median 392).</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3991,11 +3991,11 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Dr. Sourabh Pal (592)</t>
+          <t>Paramarsh Bharti (994)</t>
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>179</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik 1382 vs our median 99).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Best Career Counselling 948 vs our median 33).</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -4034,11 +4034,11 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Sai Santosh Spine Cure centre--Ayush Height clinic=Dr Mitke| Best Ayurvedic Doctor in Nashik | spine specialist In Nashik (1382)</t>
+          <t>Best Career Counselling (948)</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Tumkur</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Dr. Bakhru's 2214 vs our median 2).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Siddaganga Medical College &amp; Research Institute 1139 vs our median 0).</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -4077,11 +4077,11 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Dr. Bakhru's (2214)</t>
+          <t>Siddaganga Medical College &amp; Research Institute (1139)</t>
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot 1479 vs our median 0).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC 1150 vs our median 15).</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -4120,11 +4120,11 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
+          <t>Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC (1150)</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Paramarsh Bharti 994 vs our median 392).</t>
+          <t>No paid spend. 1/1 clinics out-reviewed (top rival Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag 720 vs our median 41).</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4163,182 +4163,10 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Paramarsh Bharti (994)</t>
+          <t>Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag (720)</t>
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="85" ht="40" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Mental Health</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>ORGANIC</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Reviews / GMB</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Best Career Counselling 948 vs our median 33).</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>Best Career Counselling (948)</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>Mental Health</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Tumkur</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>ORGANIC</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>Reviews / GMB</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Siddaganga Medical College &amp; Research Institute 1139 vs our median 0).</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>Siddaganga Medical College &amp; Research Institute (1139)</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="40" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Mental Health</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>ORGANIC</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Reviews / GMB</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC 1150 vs our median 15).</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>Psychiatrist Dr Kritagnasinh vaghela JAY CLINIC (1150)</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" ht="40" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Mental Health</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Visakhapatnam</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>ORGANIC</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Reviews / GMB</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>No paid spend. 1/1 clinics out-reviewed (top rival Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag 720 vs our median 41).</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>Travancore Ayurveda NABH Panchakarma Clinic | MVP Colony | Vizag (720)</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="n">
         <v>41</v>
       </c>
     </row>
@@ -6982,7 +6810,7 @@
         <v>19.9</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
@@ -7053,7 +6881,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
@@ -7124,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
@@ -7266,7 +7094,7 @@
         <v>7</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
@@ -7408,7 +7236,7 @@
         <v>6</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
@@ -7479,7 +7307,7 @@
         <v>544</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
@@ -7621,7 +7449,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
@@ -7692,7 +7520,7 @@
         <v>13.1</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
@@ -7834,7 +7662,7 @@
         <v>127.9</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
@@ -7905,7 +7733,7 @@
         <v>21.4</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
@@ -8118,7 +7946,7 @@
         <v>1.5</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
@@ -8331,7 +8159,7 @@
         <v>330.7</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
@@ -8544,7 +8372,7 @@
         <v>4.9</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
@@ -9167,7 +8995,7 @@
         <v>40</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
@@ -9238,7 +9066,7 @@
         <v>64.2</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
@@ -9309,7 +9137,7 @@
         <v>28</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
@@ -9380,7 +9208,7 @@
         <v>12.2</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
@@ -9451,7 +9279,7 @@
         <v>4.6</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
@@ -9522,7 +9350,7 @@
         <v>39.9</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
@@ -9593,7 +9421,7 @@
         <v>37.6</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
@@ -9664,7 +9492,7 @@
         <v>1.4</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
@@ -9735,7 +9563,7 @@
         <v>544</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
@@ -9806,7 +9634,7 @@
         <v>37.8</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
@@ -9877,7 +9705,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
@@ -9948,7 +9776,7 @@
         <v>49.9</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
@@ -10019,7 +9847,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
@@ -10090,7 +9918,7 @@
         <v>35.2</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
@@ -10161,7 +9989,7 @@
         <v>4.7</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
@@ -10232,7 +10060,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
@@ -10303,7 +10131,7 @@
         <v>13.8</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
@@ -10445,7 +10273,7 @@
         <v>20.5</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
@@ -10516,11 +10344,11 @@
         <v>137.7</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
+          <t>Holding on reviews organically.</t>
         </is>
       </c>
     </row>
@@ -10855,11 +10683,11 @@
         <v>320</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
+          <t>Holding on reviews organically.</t>
         </is>
       </c>
     </row>
@@ -10997,11 +10825,11 @@
         <v>1.9</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
+          <t>Holding on reviews organically.</t>
         </is>
       </c>
     </row>
@@ -11139,11 +10967,11 @@
         <v>99.8</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>Organic/GMB market — build reviews &amp; GMB before/instead of paid.</t>
+          <t>Holding on reviews organically.</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11180,7 @@
         <v>23.1</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
@@ -11423,7 +11251,7 @@
         <v>11.3</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
@@ -11494,7 +11322,7 @@
         <v>36.9</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
@@ -11707,7 +11535,7 @@
         <v>29.9</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
@@ -13473,7 +13301,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (1062 vs 29)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1062 vs 29)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -13523,7 +13351,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (435 vs 3)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (435 vs 3)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -13573,7 +13401,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (259 vs 53)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (259 vs 53)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -13621,12 +13449,12 @@
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13721,12 +13549,12 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13769,12 +13597,12 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13697,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (931 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (931 vs 9)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -13919,7 +13747,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Unani rival leads 536 vs 492</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (536 vs 492)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -14069,7 +13897,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (616 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (616 vs 9)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -14217,7 +14045,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (1396 vs 47)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1396 vs 47)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -14267,7 +14095,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (828 vs 47)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (828 vs 47)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -14317,7 +14145,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (1396 vs 478)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1396 vs 478)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -14465,7 +14293,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopathic rival far ahead (1078 vs 16)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1078 vs 16)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -14563,7 +14391,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (2242 vs 594)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2242 vs 594)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -14713,7 +14541,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (924 vs 320)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (924 vs 320)</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -14813,7 +14641,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (149 vs 44)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (149 vs 44)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -14963,7 +14791,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (57 vs 15)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (57 vs 15)</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -15063,7 +14891,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Unani rival far ahead (2119 vs 947)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2119 vs 947)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -15113,7 +14941,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Unani rival far ahead (2119 vs 947)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2119 vs 947)</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -15209,7 +15037,7 @@
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 354 vs 329</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (354 vs 329)</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -15259,7 +15087,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (467 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (467 vs 9)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -15309,7 +15137,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopathic rival far ahead (1016 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1016 vs 9)</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -15359,12 +15187,12 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15237,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (2375 vs 187)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2375 vs 187)</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -15459,7 +15287,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 354 vs 329</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (354 vs 329)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -15705,7 +15533,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (536 vs 90)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (536 vs 90)</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
@@ -15899,7 +15727,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Unani rival leads 256 vs 168</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (256 vs 168)</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
@@ -16047,12 +15875,12 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -16297,12 +16125,12 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16675,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (248 vs 81)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (248 vs 81)</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -16897,12 +16725,12 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16775,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (2139 vs 449)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2139 vs 449)</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -17097,7 +16925,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopathic rival far ahead (1775 vs 356)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1775 vs 356)</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -17147,7 +16975,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (865 vs 305)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (865 vs 305)</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -17295,12 +17123,12 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17173,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (706 vs 33)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (706 vs 33)</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -17443,7 +17271,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (1919 vs 15)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1919 vs 15)</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -17643,7 +17471,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (15775 vs 29)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (15775 vs 29)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -17693,7 +17521,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Fertility clinic rival far ahead (413 vs 3)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (413 vs 3)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -17841,7 +17669,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Fertility clinic rival far ahead (884 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (884 vs 9)</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -17891,7 +17719,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1932 vs 338)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1932 vs 338)</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -17991,7 +17819,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (6449 vs 655)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (6449 vs 655)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -18041,7 +17869,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 492)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (18997 vs 492)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -18091,7 +17919,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 45)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (18997 vs 45)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -18141,7 +17969,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 338)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (18997 vs 338)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -18191,7 +18019,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (5744 vs 385)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (5744 vs 385)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -18241,7 +18069,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (842 vs 198)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (842 vs 198)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -18291,7 +18119,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (18997 vs 338)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (18997 vs 338)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -18389,7 +18217,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 627)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (21686 vs 627)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -18439,7 +18267,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 47)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (21686 vs 47)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -18489,7 +18317,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (21686 vs 47)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (21686 vs 47)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -18539,7 +18367,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (1396 vs 478)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1396 vs 478)</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -18589,7 +18417,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival leads 861 vs 604</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (861 vs 604)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -18687,7 +18515,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (1078 vs 16)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1078 vs 16)</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -18785,7 +18613,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical laboratory rival far ahead (1238 vs 594)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1238 vs 594)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -18835,7 +18663,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical laboratory rival far ahead (1238 vs 320)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1238 vs 320)</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -18885,7 +18713,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (851 vs 3)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (851 vs 3)</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -18935,7 +18763,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (4337 vs 320)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4337 vs 320)</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -18985,7 +18813,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (8968 vs 148)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (8968 vs 148)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -19035,7 +18863,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1190 vs 44)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1190 vs 44)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -19085,7 +18913,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (6775 vs 594)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (6775 vs 594)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -19135,7 +18963,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Blood testing service rival leads 413 vs 288</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (413 vs 288)</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -19185,7 +19013,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — General hospital rival far ahead (567 vs 15)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (567 vs 15)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -19235,7 +19063,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Doctor rival far ahead (635 vs 31)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (635 vs 31)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -19285,7 +19113,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (10590 vs 947)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (10590 vs 947)</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -19335,7 +19163,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (4637 vs 947)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4637 vs 947)</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -19383,7 +19211,7 @@
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (1459 vs 10)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1459 vs 10)</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -19431,7 +19259,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (6238 vs 329)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (6238 vs 329)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -19481,7 +19309,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1894 vs 438)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1894 vs 438)</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -19531,7 +19359,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (3827 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (3827 vs 9)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -19581,7 +19409,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (4992 vs 990)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4992 vs 990)</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -19631,7 +19459,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (2134 vs 187)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2134 vs 187)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -19779,7 +19607,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (7413 vs 73)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (7413 vs 73)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -19829,7 +19657,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (9270 vs 73)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (9270 vs 73)</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
@@ -19927,7 +19755,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (1096 vs 90)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1096 vs 90)</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
@@ -20121,7 +19949,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (785 vs 168)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (785 vs 168)</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
@@ -20171,7 +19999,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival leads 1066 vs 712</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1066 vs 712)</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -20221,7 +20049,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (1228 vs 380)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1228 vs 380)</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -20319,7 +20147,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (15414 vs 382)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (15414 vs 382)</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -20369,7 +20197,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (6925 vs 495)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (6925 vs 495)</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -20469,7 +20297,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (15414 vs 197)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (15414 vs 197)</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -20519,7 +20347,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival leads 803 vs 550</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (803 vs 550)</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -20619,7 +20447,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (488 vs 10)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (488 vs 10)</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -20669,7 +20497,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival leads 563 vs 515</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (563 vs 515)</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -20769,7 +20597,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical clinic rival far ahead (4866 vs 550)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4866 vs 550)</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -20819,7 +20647,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Sexologist rival far ahead (1566 vs 179)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1566 vs 179)</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -20869,7 +20697,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical clinic rival far ahead (4937 vs 99)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4937 vs 99)</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -20919,7 +20747,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical diagnostic imaging center rival far ahead (1045 vs 260)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1045 vs 260)</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -20969,7 +20797,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (691 vs 66)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (691 vs 66)</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
@@ -21019,7 +20847,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — STD testing service rival far ahead (1202 vs 380)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1202 vs 380)</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -21069,7 +20897,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopath rival far ahead (704 vs 81)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (704 vs 81)</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -21169,7 +20997,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (11472 vs 449)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (11472 vs 449)</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -21269,7 +21097,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (2991 vs 330)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2991 vs 330)</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -21319,7 +21147,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (3234 vs 356)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (3234 vs 356)</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -21369,7 +21197,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical laboratory rival far ahead (4987 vs 305)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (4987 vs 305)</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -21419,7 +21247,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival far ahead (640 vs 2)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (640 vs 2)</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -21517,7 +21345,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Diagnostic center rival leads 761 vs 392</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (761 vs 392)</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -21567,7 +21395,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — HIV testing center rival far ahead (1162 vs 33)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1162 vs 33)</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -21665,7 +21493,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopath rival far ahead (1497 vs 15)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1497 vs 15)</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -21715,7 +21543,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Specialized clinic rival far ahead (567 vs 41)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (567 vs 41)</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -22313,7 +22141,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Medical clinic rival leads 757 vs 746</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (757 vs 746)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -22811,7 +22639,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital rival leads 719 vs 604</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (719 vs 604)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -23357,7 +23185,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (3253 vs 288)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (3253 vs 288)</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -23457,7 +23285,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Psychiatrist rival far ahead (928 vs 31)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (928 vs 31)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -24591,12 +24419,12 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -24991,12 +24819,12 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25219,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Hospital rival far ahead (11251 vs 449)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (11251 vs 449)</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">

--- a/Competition_Action_Plan.xlsx
+++ b/Competition_Action_Plan.xlsx
@@ -675,16 +675,16 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (655 vs 260 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (623 vs 186 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Dr Ajinkya Patil (655)</t>
+          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai (623)</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>260</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
@@ -695,7 +695,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -708,26 +708,26 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Bid / Budget ↑</t>
+          <t>Budget / Bid + Reviews</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>IS 69% · Loc→Lead 18% · Lead→Book 77% · CPL ₹162</t>
+          <t>IS 55% · Loc→Lead 18% · Lead→Book 73% · CPL ₹112</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 69%) but map clicks don't convert (18%); rival Unani 256 vs our 168 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Thin 842 vs our 336 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Dr Khokar (256)</t>
+          <t>Dr Suresh Damodharan (842)</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>168</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
@@ -738,7 +738,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -756,21 +756,21 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>IS 68% · Loc→Lead 13% · Lead→Book 77% · CPL ₹200</t>
+          <t>IS 69% · Loc→Lead 18% · Lead→Book 77% · CPL ₹162</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 68%) but map clicks don't convert (13%); rival Allopathic 236 vs our 392 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 69%) but map clicks don't convert (18%); rival Ayurvedic 256 vs our 209 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Dr. Somya Sinha (236)</t>
+          <t>Khokar Dispensary (256)</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>392</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 385 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 261 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>385</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
@@ -1105,16 +1105,16 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Allopathic 2375 vs our 258 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Unani 3300 vs our 105 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Androcare Andrology Institute (2375)</t>
+          <t>Care and Cure (3300)</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>258</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
@@ -1148,16 +1148,16 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Ayurvedic rival (7034 vs 386 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Ayurvedic rival (7100 vs 372 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Dr Yogendra Rai (7034)</t>
+          <t>Dr Yogendra Rai (7100)</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>386</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
@@ -1234,16 +1234,16 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2242 vs 320 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (923 vs 36 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>A4 Hospital (2242)</t>
+          <t>Dr. Kamaraj Hospital (923)</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>320</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
@@ -1277,16 +1277,16 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2139 vs 305 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Homeopathic rival (1800 vs 263 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Kidney And Urology Super Speciality Institute Hospital (2139)</t>
+          <t>Vanad Clinic (1800)</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 15776 vs our 29 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 805 vs our 45 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>GIPS Hospital and De-addiction Centre (15776)</t>
+          <t>Dr Kalrav mistry (805)</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (992 vs 3 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (435 vs 20 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>𝗦𝗮𝗺𝗮𝗿𝘁𝗵 𝗦𝘂𝗽𝗲𝗿 -Specialty Heart Hospital-Cardiologist/Heart Specialist/Physician/Best Hospital in Amravati (992)</t>
+          <t>Dr. Vishal Bahekar | Urologist | Amravati (435)</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -1444,21 +1444,21 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>IS 55% · Loc→Lead 18% · Lead→Book 73% · CPL ₹112</t>
+          <t>IS 52% · Loc→Lead 12% · Lead→Book 71% · CPL ₹239</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Allopathic 3253 vs our 288 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Ayurvedic 298 vs our 11 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Vazhikatti Mental Health Centre &amp; Research Institute (3253)</t>
+          <t>Dr. Maratha Clinic | Sexual Health Expert (298)</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>288</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Hubli</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1487,21 +1487,21 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>IS 52% · Loc→Lead 12% · Lead→Book 71% · CPL ₹239</t>
+          <t>IS 63% · Loc→Lead 19% · Lead→Book 68% · CPL ₹217</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Allopathic 196 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1200 vs our 35 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Navkar Clinic &amp; Health Care (196)</t>
+          <t>Dr Shambhu K MBBS, MS, MCh, F MAS Urologist &amp; Andrologist, Laparoscopic &amp; Transplant Surgeon (1200)</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Hubli</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -1530,21 +1530,21 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>IS 63% · Loc→Lead 19% · Lead→Book 68% · CPL ₹217</t>
+          <t>IS 45% · Loc→Lead 14% · Lead→Book 52% · CPL ₹228</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1207 vs our 31 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 1500 vs our 112 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Dr Shambhu K MBBS, MS, MCh, F MAS Urologist &amp; Andrologist, Laparoscopic &amp; Transplant Surgeon (1207)</t>
+          <t>Dr. Amit Joshi (1500)</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -1573,21 +1573,21 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>IS 45% · Loc→Lead 14% · Lead→Book 52% · CPL ₹228</t>
+          <t>IS 57% · Loc→Lead 10% · Lead→Book 82% · CPL ₹270</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 536 vs our 90 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1600 vs our 217 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kapil Sharma - Best Psychiatrist in Jaipur | Best Psychologist in Jaipur (536)</t>
+          <t>Krisham Health Care (1600)</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>90</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -1616,21 +1616,21 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>IS 57% · Loc→Lead 10% · Lead→Book 82% · CPL ₹270</t>
+          <t>IS 54% · Loc→Lead 8% · Lead→Book 64% · CPL ₹479</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1565 vs our 179 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 388 vs our 2 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Krisham Men's Health (Sexology) And Diabetis Clinic (1565)</t>
+          <t>Shri Mahaveer Hospital (388)</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>179</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1659,21 +1659,21 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>IS 54% · Loc→Lead 8% · Lead→Book 64% · CPL ₹479</t>
+          <t>IS 68% · Loc→Lead 13% · Lead→Book 77% · CPL ₹200</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 535 vs our 2 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 68%) but map clicks don't convert (13%); rival Allopathic 2400 vs our 446 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Skinroots (535)</t>
+          <t>Stone And Urology Clinic (2400)</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
@@ -1702,21 +1702,21 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>IS 57% · Loc→Lead 1% · Lead→Book 100% · CPL ₹3231</t>
+          <t>IS 58% · Loc→Lead 12% · Lead→Book 63% · CPL ₹134</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (1%); rival Allopathic 1479 vs our 0 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Allopathic 747 vs our 34 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
+          <t>Dr Anuj Khandelwal (747)</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -1745,21 +1745,21 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>IS 58% · Loc→Lead 12% · Lead→Book 63% · CPL ₹134</t>
+          <t>IS 58% · Loc→Lead 22% · Lead→Book 76% · CPL ₹178</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Ayurvedic 706 vs our 33 reviews wins the listing. Scale + build reviews.</t>
+          <t>Map clicks leak — listing loses to Ayurvedic rival (186 vs 35 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Kalptaru Ayurvedam (706)</t>
+          <t>Ayushri Ayurveda - 45y Exp Doctor (Govt-rtd) (186)</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>IS 58% · Loc→Lead 22% · Lead→Book 76% · CPL ₹178</t>
+          <t>IS 57% · Loc→Lead 1% · Lead→Book 100% · CPL ₹3231</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (875 vs 41 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (1%); rival Allopathic 1479 vs our 0 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Dr. M Prasada Rao (875)</t>
+          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot (1479)</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (259 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (259 vs 52 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
@@ -2180,16 +2180,16 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (480 vs 550 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (481 vs 731 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Prerana Psychiatry &amp; Gynaecology Hospital (480)</t>
+          <t>Prerana Psychiatry &amp; Gynaecology Hospital (481)</t>
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>550</v>
+        <v>731</v>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
@@ -2309,16 +2309,16 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 56%) but map clicks don't convert (15%); rival Homeopathic 1078 vs our 16 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 56%) but map clicks don't convert (15%); rival Homeopathic 1100 vs our 11 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Dr Diwakar's Clinic (1078)</t>
+          <t>Dr Diwakar's Clinic (1100)</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
@@ -2352,16 +2352,16 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 50%) but map clicks don't convert (13%); rival Ayurvedic 5126 vs our 99 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 50%) but map clicks don't convert (13%); rival Ayurvedic 5100 vs our 138 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Urja Ayurved Centre (5126)</t>
+          <t>Urja Ayurved Centre (5100)</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 45%) but map clicks don't convert (6%); rival Allopathic 1919 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 45%) but map clicks don't convert (6%); rival Allopathic 1200 vs our 15 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Aashray Urology Institute (1919)</t>
+          <t>Psychiatrist - Dr. Parth A Soni -Alpha Mind Clinic- Sexologist (1200)</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>655 vs 260 (3×)</t>
+          <t>623 vs 186 (3×)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>IS 61% room, gap 2.5× — raise budget/bid + build reviews</t>
+          <t>IS 61% room, gap 3.3× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4331,37 +4331,37 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2131</v>
+        <v>1752</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.128</v>
+        <v>0.178</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.766</v>
+        <v>0.734</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>533</v>
+        <v>250</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>236 vs 392 (1×)</t>
+          <t>842 vs 336 (3×)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Bid / Budget ↑</t>
+          <t>Budget / Bid + Reviews</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Gap coverable (0.6×) + IS 68% room — bid/profile push can win the click while reviews catch up</t>
+          <t>IS 55% room, gap 2.5× — raise budget/bid + build reviews</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>256 vs 168 (2×)</t>
+          <t>256 vs 209 (1×)</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Gap coverable (1.5×) + IS 69% room — bid/profile push can win the click while reviews catch up</t>
+          <t>Gap coverable (1.2×) + IS 69% room — bid/profile push can win the click while reviews catch up</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>7670 vs 385 (20×)</t>
+          <t>7670 vs 261 (29×)</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 20× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 29× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>2375 vs 258 (9×)</t>
+          <t>3300 vs 105 (31×)</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 9× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 31× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>2139 vs 305 (7×)</t>
+          <t>1800 vs 263 (7×)</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>7034 vs 386 (18×)</t>
+          <t>7100 vs 372 (19×)</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 18× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 19× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>2242 vs 320 (7×)</t>
+          <t>923 vs 36 (26×)</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 7× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 26× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>536 vs 90 (6×)</t>
+          <t>1500 vs 112 (13×)</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 6× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 13× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>15776 vs 29 (544×)</t>
+          <t>805 vs 45 (18×)</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 544× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 18× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>1565 vs 179 (9×)</t>
+          <t>1600 vs 217 (7×)</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 9× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 7× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>196 vs 15 (13×)</t>
+          <t>298 vs 11 (27×)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 13× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 27× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5285,27 +5285,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>1854</v>
+        <v>2131</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0.585</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>0.627</v>
+        <v>0.128</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>0.766</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>371</v>
+        <v>533</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>706 vs 33 (21×)</t>
+          <t>2400 vs 446 (5×)</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 21× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 5× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5332,27 +5332,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>1752</v>
+        <v>1854</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.547</v>
+        <v>0.585</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="G28" s="17" t="n">
-        <v>0.734</v>
+        <v>0.12</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>0.627</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>250</v>
+        <v>371</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>3253 vs 288 (11×)</t>
+          <t>747 vs 34 (22×)</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 11× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 22× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>875 vs 41 (21×)</t>
+          <t>186 vs 35 (5×)</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 21× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 5× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>535 vs 2 (268×)</t>
+          <t>388 vs 2 (194×)</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 268× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 194× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>992 vs 3 (331×)</t>
+          <t>435 vs 20 (22×)</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 331× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 22× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>1207 vs 31 (39×)</t>
+          <t>1200 vs 35 (34×)</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Rival out-reviews us 39× — too heavy to win on ads; build reviews, don't push bid here</t>
+          <t>Rival out-reviews us 34× — too heavy to win on ads; build reviews, don't push bid here</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>480 vs 550 (1×)</t>
+          <t>481 vs 731 (1×)</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>259 vs 53 (5×)</t>
+          <t>259 vs 52 (5×)</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>1078 vs 16 (67×)</t>
+          <t>1100 vs 11 (100×)</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>1919 vs 15 (128×)</t>
+          <t>1200 vs 15 (80×)</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>5126 vs 99 (52×)</t>
+          <t>5100 vs 138 (37×)</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -6791,7 +6791,7 @@
         <v>0.735</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>385</v>
+        <v>261</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
@@ -6807,14 +6807,14 @@
         <v>7670</v>
       </c>
       <c r="Q3" s="26" t="n">
-        <v>19.9</v>
+        <v>29.4</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 385 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (19%); rival Allopathic 7670 vs our 261 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
@@ -6862,30 +6862,30 @@
         <v>0.726</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>258</v>
+        <v>105</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Androcare Andrology Institute</t>
+          <t>Care and Cure</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="P4" s="4" t="n">
-        <v>2375</v>
+        <v>3300</v>
       </c>
       <c r="Q4" s="26" t="n">
-        <v>9.199999999999999</v>
+        <v>31.4</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Allopathic 2375 vs our 258 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (17%); rival Unani 3300 vs our 105 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -6933,30 +6933,30 @@
         <v>0.755</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Kidney And Urology Super Speciality Institute Hospital</t>
+          <t>Vanad Clinic</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Homeopathic</t>
         </is>
       </c>
       <c r="P5" s="4" t="n">
-        <v>2139</v>
+        <v>1800</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2139 vs 305 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Homeopathic rival (1800 vs 263 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
         <v>0.731</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -7017,17 +7017,17 @@
         </is>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7034</v>
+        <v>7100</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>18.2</v>
+        <v>19.1</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Ayurvedic rival (7034 vs 386 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Ayurvedic rival (7100 vs 372 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -7075,11 +7075,11 @@
         <v>0.766</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>320</v>
+        <v>36</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>A4 Hospital</t>
+          <t>Dr. Kamaraj Hospital</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
@@ -7088,17 +7088,17 @@
         </is>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2242</v>
+        <v>923</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>7</v>
+        <v>25.6</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (2242 vs 320 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (923 vs 36 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -7146,11 +7146,11 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>260</v>
+        <v>186</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Dr Ajinkya Patil</t>
+          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
@@ -7159,17 +7159,17 @@
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>655</v>
-      </c>
-      <c r="Q8" s="27" t="n">
-        <v>2.5</v>
+        <v>623</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <v>3.3</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (655 vs 260 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (623 vs 186 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -7217,11 +7217,11 @@
         <v>0.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kapil Sharma - Best Psychiatrist in Jaipur | Best Psychologist in Jaipur</t>
+          <t>Dr. Amit Joshi</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
@@ -7230,17 +7230,17 @@
         </is>
       </c>
       <c r="P9" s="4" t="n">
-        <v>536</v>
+        <v>1500</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>6</v>
+        <v>13.4</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 536 vs our 90 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 45%) but map clicks don't convert (14%); rival Allopathic 1500 vs our 112 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7288,11 +7288,11 @@
         <v>0.581</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>GIPS Hospital and De-addiction Centre</t>
+          <t>Dr Kalrav mistry</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
@@ -7301,17 +7301,17 @@
         </is>
       </c>
       <c r="P10" s="4" t="n">
-        <v>15776</v>
+        <v>805</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>544</v>
+        <v>17.9</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 15776 vs our 29 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 46%) but map clicks don't convert (9%); rival Allopathic 805 vs our 45 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7359,11 +7359,11 @@
         <v>0.609</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>Krisham Men's Health (Sexology) And Diabetis Clinic</t>
+          <t>Krisham Health Care</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
@@ -7372,17 +7372,17 @@
         </is>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1565</v>
+        <v>1600</v>
       </c>
       <c r="Q11" s="26" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1565 vs our 179 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 57%) but map clicks don't convert (10%); rival Allopathic 1600 vs our 217 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
         <v>0.417</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -7443,17 +7443,17 @@
         </is>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1078</v>
+        <v>1100</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>67.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 56%) but map clicks don't convert (15%); rival Homeopathic 1078 vs our 16 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 56%) but map clicks don't convert (15%); rival Homeopathic 1100 vs our 11 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7501,30 +7501,30 @@
         <v>0.641</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Navkar Clinic &amp; Health Care</t>
+          <t>Dr. Maratha Clinic | Sexual Health Expert</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>13.1</v>
+        <v>27.1</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Allopathic 196 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 52%) but map clicks don't convert (12%); rival Ayurvedic 298 vs our 11 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
       <c r="B14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>INVEST ↑</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>FIX PROFILE FIRST</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Bid / Budget ↑</t>
+          <t>Reviews (not bid)</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
@@ -7572,11 +7572,11 @@
         <v>0.551</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Dr. Somya Sinha</t>
+          <t>Stone And Urology Clinic</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -7585,17 +7585,17 @@
         </is>
       </c>
       <c r="P14" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0.6</v>
+        <v>2400</v>
+      </c>
+      <c r="Q14" s="26" t="n">
+        <v>5.4</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 68%) but map clicks don't convert (13%); rival Allopathic 236 vs our 392 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 68%) but map clicks don't convert (13%); rival Allopathic 2400 vs our 446 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>Aashray Urology Institute</t>
+          <t>Psychiatrist - Dr. Parth A Soni -Alpha Mind Clinic- Sexologist</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -7656,17 +7656,17 @@
         </is>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1919</v>
+        <v>1200</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>127.9</v>
+        <v>80</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 45%) but map clicks don't convert (6%); rival Allopathic 1919 vs our 15 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 45%) but map clicks don't convert (6%); rival Allopathic 1200 vs our 15 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7714,30 +7714,30 @@
         <v>0.577</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Kalptaru Ayurvedam</t>
+          <t>Dr Anuj Khandelwal</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
-        <v>706</v>
+        <v>747</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Ayurvedic 706 vs our 33 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 58%) but map clicks don't convert (12%); rival Allopathic 747 vs our 34 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7750,14 +7750,14 @@
       <c r="B17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>FIX PROFILE FIRST</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>INVEST ↑</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Reviews (not bid)</t>
+          <t>Budget / Bid + Reviews</t>
         </is>
       </c>
       <c r="E17" s="15" t="n">
@@ -7785,30 +7785,30 @@
         <v>0.623</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Vazhikatti Mental Health Centre &amp; Research Institute</t>
+          <t>Dr Suresh Damodharan</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3253</v>
-      </c>
-      <c r="Q17" s="26" t="n">
-        <v>11.3</v>
+        <v>842</v>
+      </c>
+      <c r="Q17" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Allopathic 3253 vs our 288 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 55%) but map clicks don't convert (18%); rival Thin 842 vs our 336 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7856,30 +7856,30 @@
         <v>0.675</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Dr. M Prasada Rao</t>
+          <t>Ayushri Ayurveda - 45y Exp Doctor (Govt-rtd)</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
-        <v>875</v>
+        <v>186</v>
       </c>
       <c r="Q18" s="26" t="n">
-        <v>21.3</v>
+        <v>5.3</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (875 vs 41 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Ayurvedic rival (186 vs 35 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -7927,30 +7927,30 @@
         <v>0.806</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Dr Khokar</t>
+          <t>Khokar Dispensary</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>Unani</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
         <v>256</v>
       </c>
-      <c r="Q19" s="27" t="n">
-        <v>1.5</v>
+      <c r="Q19" s="4" t="n">
+        <v>1.2</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 69%) but map clicks don't convert (18%); rival Unani 256 vs our 168 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 69%) but map clicks don't convert (18%); rival Ayurvedic 256 vs our 209 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
         <v>0.706</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -8011,17 +8011,17 @@
         </is>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5126</v>
+        <v>5100</v>
       </c>
       <c r="Q20" s="26" t="n">
-        <v>51.8</v>
+        <v>37</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 50%) but map clicks don't convert (13%); rival Ayurvedic 5126 vs our 99 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 50%) but map clicks don't convert (13%); rival Ayurvedic 5100 vs our 138 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Skinroots</t>
+          <t>Shri Mahaveer Hospital</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -8082,17 +8082,17 @@
         </is>
       </c>
       <c r="P21" s="4" t="n">
-        <v>535</v>
+        <v>388</v>
       </c>
       <c r="Q21" s="26" t="n">
-        <v>267.5</v>
+        <v>194</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 535 vs our 2 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 54%) but map clicks don't convert (8%); rival Allopathic 388 vs our 2 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -8140,11 +8140,11 @@
         <v>0.25</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>𝗦𝗮𝗺𝗮𝗿𝘁𝗵 𝗦𝘂𝗽𝗲𝗿 -Specialty Heart Hospital-Cardiologist/Heart Specialist/Physician/Best Hospital in Amravati</t>
+          <t>Dr. Vishal Bahekar | Urologist | Amravati</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -8153,17 +8153,17 @@
         </is>
       </c>
       <c r="P22" s="4" t="n">
-        <v>992</v>
+        <v>435</v>
       </c>
       <c r="Q22" s="26" t="n">
-        <v>330.7</v>
+        <v>21.8</v>
       </c>
       <c r="R22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (992 vs 3 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (435 vs 20 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
         <v>0.581</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>550</v>
+        <v>731</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -8224,17 +8224,17 @@
         </is>
       </c>
       <c r="P23" s="4" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="R23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (480 vs 550 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (481 vs 731 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
         <v>0.529</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -8295,17 +8295,17 @@
         </is>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="Q24" s="26" t="n">
-        <v>38.9</v>
+        <v>34.3</v>
       </c>
       <c r="R24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1207 vs our 31 reviews wins the listing. Scale + build reviews.</t>
+          <t>Room to scale (IS 63%) but map clicks don't convert (19%); rival Allopathic 1200 vs our 35 reviews wins the listing. Scale + build reviews.</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -8369,14 +8369,14 @@
         <v>259</v>
       </c>
       <c r="Q25" s="26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>Map clicks leak — listing loses to Allopathic rival (259 vs 53 reviews). Build reviews / GMB, don't just raise budget.</t>
+          <t>Map clicks leak — listing loses to Allopathic rival (259 vs 52 reviews). Build reviews / GMB, don't just raise budget.</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13272,41 +13272,41 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Dr. Mrugesh Vaishnav</t>
+          <t>Dr. Maratha Clinic | Sexual Health Expert</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G3" s="26" t="n">
-        <v>-1033</v>
+        <v>298</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>-253</v>
       </c>
       <c r="H3" s="26" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J3" s="15" t="n">
         <v>2378</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1062 vs 29)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (298 vs 45)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1033 to match)</t>
+          <t>Build reviews (need +253 to match)</t>
         </is>
       </c>
     </row>
@@ -13322,11 +13322,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vishal Bahekar | Urologist | Amravati</t>
+          <t>AshaKiran Clinic | Sexologist in Amravati | Best Sexologist</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -13335,28 +13335,28 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>435</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>-432</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.01</v>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J4" s="15" t="n">
         <v>164</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (435 vs 3)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +432 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13372,11 +13372,11 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Deep Clinic</t>
+          <t>Dr. Renuka Alsi Loya - Gynecologist and Sexologist in Aurangabad(Chh.Sambhajinagar)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -13385,28 +13385,28 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>259</v>
+        <v>102</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>-206</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.2</v>
+        <v>-50</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>0.51</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="15" t="n">
         <v>1493</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (259 vs 53)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (102 vs 52)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +206 to match)</t>
+          <t>Build reviews (need +50 to match)</t>
         </is>
       </c>
     </row>
@@ -13520,41 +13520,39 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>842</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Dr Anantharaman's clinic</t>
+          <t>Dr Lohit's Ayur Clinic</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>616</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>226</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>-1400</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="15" t="n">
         <v>1447</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (1400 vs 0)</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +1400 to match)</t>
         </is>
       </c>
     </row>
@@ -13668,11 +13666,11 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9</v>
+        <v>1100</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>SS (Shree Srinivasa) Uro Care | Dr. Shiva Kumar | Urology Hospital Bangalore</t>
+          <t>Dr. Khokar Men's Health Clinic</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -13681,28 +13679,28 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>931</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>-922</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>0.01</v>
+        <v>528</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>572</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>2.08</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>4398</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (931 vs 9)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +922 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13718,41 +13716,39 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>492</v>
+        <v>904</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Ristar wellness clinic</t>
+          <t>Dr. Khokar Men's Health Clinic</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Unani</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>536</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1.7</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>376</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="15" t="n">
         <v>4369</v>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (536 vs 492)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +44 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -13768,11 +13764,11 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>385</v>
+        <v>257</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Dr Madhusudhan Naidu</t>
+          <t>Medi Life Health Care - Sexologist Clinic</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -13781,17 +13777,15 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="G13" s="28" t="n">
-        <v>357</v>
+        <v>156</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>6.6</v>
-      </c>
+        <v>2.54</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="15" t="n">
         <v>1812</v>
       </c>
@@ -13818,11 +13812,11 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>198</v>
+        <v>261</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Dr Karthik K N</t>
+          <t>Sexologist HIV PEP STD</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -13831,16 +13825,16 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>678</v>
@@ -13868,11 +13862,11 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Dr Anantharaman's clinic</t>
+          <t>Dr. Khokar Men's Health Clinic</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -13881,28 +13875,26 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>616</v>
+        <v>528</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>-607</v>
+        <v>-528</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>2.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="15" t="n">
         <v>3897</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (616 vs 9)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (528 vs 0)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +607 to match)</t>
+          <t>Build reviews (need +528 to match)</t>
         </is>
       </c>
     </row>
@@ -13966,41 +13958,41 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>627</v>
+        <v>53</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Ayush Health Clinic</t>
+          <t>Dr. Khokar Men's Health Clinic</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Unani</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>452</v>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>175</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>1.39</v>
+        <v>528</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-475</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>237</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>BUILD REVIEWS — Allopathic rival far ahead (528 vs 53)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +475 to match)</t>
         </is>
       </c>
     </row>
@@ -14016,41 +14008,41 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Dr Lohit's Ayur Clinic</t>
+          <t>Sagar Dispensary - Best Sexologist in Bangalore | Sex Clinic | Sex Doctor</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1396</v>
+        <v>563</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-1349</v>
+        <v>-553</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>364</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1396 vs 47)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (563 vs 10)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1349 to match)</t>
+          <t>Build reviews (need +553 to match)</t>
         </is>
       </c>
     </row>
@@ -14066,11 +14058,11 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>47</v>
+        <v>587</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Mind and Brain Hospital</t>
+          <t>Dr. Khokar Men's Health Clinic</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -14079,28 +14071,28 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>828</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>-781</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0.06</v>
+        <v>528</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>1.11</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J19" s="15" t="n">
         <v>1932</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (828 vs 47)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +781 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -14116,41 +14108,41 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>478</v>
+        <v>344</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Dr Lohit's Ayur Clinic</t>
+          <t>Sexologist HIV PEP STD</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1396</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-918</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.34</v>
+        <v>131</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>213</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>2.63</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>2773</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1396 vs 478)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +918 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14158,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>604</v>
+        <v>819</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -14182,14 +14174,12 @@
         <v>28</v>
       </c>
       <c r="G21" s="28" t="n">
-        <v>576</v>
+        <v>791</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>3.7</v>
-      </c>
+        <v>29.25</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="15" t="n">
         <v>1520</v>
       </c>
@@ -14264,11 +14254,11 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Dr Diwakar's Clinic</t>
+          <t>Dr Rajesh's Sexology Clinic</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -14277,28 +14267,28 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1078</v>
+        <v>568</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>-1062</v>
+        <v>-557</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>1035</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1078 vs 16)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (568 vs 11)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1062 to match)</t>
+          <t>Build reviews (need +557 to match)</t>
         </is>
       </c>
     </row>
@@ -14362,11 +14352,11 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>594</v>
+        <v>2</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>A4 Hospital</t>
+          <t>Dr Shah's Clinic for Male Infertility &amp; Sexual Health</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -14375,28 +14365,28 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2242</v>
+        <v>791</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>-1648</v>
+        <v>-789</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>239</v>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (2242 vs 594)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (791 vs 2)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1648 to match)</t>
+          <t>Build reviews (need +789 to match)</t>
         </is>
       </c>
     </row>
@@ -14412,11 +14402,11 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kamaraj Hospital</t>
+          <t>Dr Shah's Clinic for Male Infertility &amp; Sexual Health</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -14425,28 +14415,28 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>924</v>
+        <v>791</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>-604</v>
+        <v>-763</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>718</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (924 vs 320)</t>
+          <t>BUILD REVIEWS — Allopathic rival far ahead (791 vs 28)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +604 to match)</t>
+          <t>Build reviews (need +763 to match)</t>
         </is>
       </c>
     </row>
@@ -14512,41 +14502,41 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kamaraj Hospital</t>
+          <t>Dr Rahman Sexual Health Clinic Sexologist Doctor Chennai</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>924</v>
-      </c>
-      <c r="G28" s="26" t="n">
-        <v>-604</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>0.35</v>
+        <v>338</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>0.9</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>5269</v>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (924 vs 320)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (338 vs 304)</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +604 to match)</t>
+          <t>Build reviews (need +34 to match)</t>
         </is>
       </c>
     </row>
@@ -14562,11 +14552,11 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Metromale Clinic &amp; Fertility Center</t>
+          <t>Blue Lotus Urology - Superspeciality Clinic for Urology, Andrology and Men's Health</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -14575,28 +14565,26 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>116</v>
-      </c>
-      <c r="H29" s="28" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>-63</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="15" t="n">
         <v>1030</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (84 vs 21)</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +63 to match)</t>
         </is>
       </c>
     </row>
@@ -14612,7 +14600,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -14628,25 +14616,25 @@
         <v>149</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H30" s="26" t="n">
         <v>0.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>2104</v>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (149 vs 44)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (149 vs 45)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +105 to match)</t>
+          <t>Build reviews (need +104 to match)</t>
         </is>
       </c>
     </row>
@@ -14662,11 +14650,11 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Urocare Kidney Stone &amp; Urologist Clinic(Dr.Neelakandan)</t>
+          <t>Dr Shah's Clinic for Male Infertility &amp; Sexual Health</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -14675,28 +14663,28 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>443</v>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>3.93</v>
+        <v>791</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>-207</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>0.74</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J31" s="15" t="n">
         <v>5652</v>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (791 vs 584)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +207 to match)</t>
         </is>
       </c>
     </row>
@@ -14712,11 +14700,11 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Harvey Skin, Hair, STD and Cosmetic Clinic</t>
+          <t>Dr Gomatthi clinic, Sexology</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -14725,28 +14713,28 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="G32" s="28" t="n">
-        <v>168</v>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>2.4</v>
+        <v>494</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>0.68</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>4262</v>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (494 vs 336)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +158 to match)</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14750,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
@@ -14775,28 +14763,28 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>-42</v>
+        <v>-49</v>
       </c>
       <c r="H33" s="26" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" s="15" t="n">
         <v>1674</v>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (57 vs 15)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (60 vs 11)</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +42 to match)</t>
+          <t>Build reviews (need +49 to match)</t>
         </is>
       </c>
     </row>
@@ -14812,41 +14800,41 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Dr Shambhu K MBBS, MS, MCh, F MAS Urologist &amp; Andrologist, Laparoscopic &amp; Transplant Surgeon</t>
+          <t>Dr. Bagalkot Sexologist</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1207</v>
-      </c>
-      <c r="G34" s="26" t="n">
-        <v>-1176</v>
+        <v>272</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>-237</v>
       </c>
       <c r="H34" s="26" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>593</v>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (1207 vs 31)</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (272 vs 35)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1176 to match)</t>
+          <t>Build reviews (need +237 to match)</t>
         </is>
       </c>
     </row>
@@ -14862,11 +14850,11 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>947</v>
+        <v>1112</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Care and Cure</t>
+          <t>DR.ALI'S SEXUAL HEALTH CLINIC</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -14875,28 +14863,28 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2119</v>
-      </c>
-      <c r="G35" s="26" t="n">
-        <v>-1172</v>
-      </c>
-      <c r="H35" s="26" t="n">
-        <v>0.45</v>
+        <v>94</v>
+      </c>
+      <c r="G35" s="28" t="n">
+        <v>1018</v>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>11.83</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>3282</v>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (2119 vs 947)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1172 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -14912,41 +14900,39 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Care and Cure</t>
+          <t>Dr Surendra Reddy Andrology</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Unani</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2119</v>
-      </c>
-      <c r="G36" s="26" t="n">
-        <v>-1172</v>
+        <v>56</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>-56</v>
       </c>
       <c r="H36" s="26" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>5.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="15" t="n">
         <v>209</v>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (2119 vs 947)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (56 vs 0)</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1172 to match)</t>
+          <t>Build reviews (need +56 to match)</t>
         </is>
       </c>
     </row>
@@ -14962,39 +14948,39 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Vasanth Poly Clinic</t>
+          <t>Sexayush Clinic | Best Sexologist in Hyderabad | Sexual health &amp; STD/STI / SEX Doctor</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1459</v>
-      </c>
-      <c r="G37" s="26" t="n">
-        <v>-1449</v>
-      </c>
-      <c r="H37" s="26" t="n">
-        <v>0.01</v>
+        <v>62</v>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>1.69</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (1459 vs 10)</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1449 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -15010,39 +14996,39 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Dr Kks uro androcare</t>
+          <t>DR.ALI'S SEXUAL HEALTH CLINIC</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>354</v>
+        <v>93</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>0.93</v>
+        <v>-93</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (354 vs 329)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (93 vs 0)</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +25 to match)</t>
+          <t>Build reviews (need +93 to match)</t>
         </is>
       </c>
     </row>
@@ -15058,11 +15044,11 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>9</v>
+        <v>1232</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Mens Clinic</t>
+          <t>Dr.Vru Clinic</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -15071,28 +15057,28 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>467</v>
-      </c>
-      <c r="G39" s="26" t="n">
-        <v>-458</v>
-      </c>
-      <c r="H39" s="26" t="n">
-        <v>0.02</v>
+        <v>53</v>
+      </c>
+      <c r="G39" s="28" t="n">
+        <v>1179</v>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>23.25</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J39" s="15" t="n">
         <v>3391</v>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (467 vs 9)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +458 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15108,41 +15094,41 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>9</v>
+        <v>374</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Spiritual Homeopathy kphb</t>
+          <t>Dr M Srinivas Rao</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Homeopathic</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1016</v>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>-1007</v>
-      </c>
-      <c r="H40" s="26" t="n">
-        <v>0.01</v>
+        <v>89</v>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>285</v>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>4.2</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>1173</v>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1016 vs 9)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1007 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15154,45 +15140,41 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Madhapur</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Spiritual Homeopathy Chandanagar</t>
+          <t>Care and Cure</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Homeopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>736</v>
-      </c>
-      <c r="G41" s="28" t="n">
-        <v>254</v>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J41" s="15" t="n">
-        <v>1280</v>
-      </c>
+        <v>2100</v>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>-2100</v>
+      </c>
+      <c r="H41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (2100 vs 0)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +2100 to match)</t>
         </is>
       </c>
     </row>
@@ -15204,45 +15186,43 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Narsingi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Androcare Andrology Institute</t>
+          <t>Rahi Ayurvedic Unani Clinic Sex Specialist</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2375</v>
-      </c>
-      <c r="G42" s="26" t="n">
-        <v>-2188</v>
-      </c>
-      <c r="H42" s="26" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>6.9</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="15" t="n">
-        <v>898</v>
+        <v>1280</v>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (2375 vs 187)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +2188 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15254,45 +15234,43 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Sainikpuri</t>
+          <t>Narsingi</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>329</v>
+        <v>396</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Dr Kks uro androcare</t>
+          <t>Care and Cure</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0.4</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>-2904</v>
+      </c>
+      <c r="H43" s="26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="15" t="n">
-        <v>2189</v>
+        <v>898</v>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (354 vs 329)</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (3300 vs 396)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +25 to match)</t>
+          <t>Build reviews (need +2904 to match)</t>
         </is>
       </c>
     </row>
@@ -15304,43 +15282,45 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Sainikpuri</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>329</v>
+        <v>173</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Dr Kks uro androcare</t>
+          <t>DR.ALI'S SEXUAL HEALTH CLINIC</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>0.93</v>
+        <v>94</v>
+      </c>
+      <c r="G44" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>1.84</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J44" s="15" t="n">
+        <v>2189</v>
+      </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 354 vs 329</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +25 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15352,15 +15332,15 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Uppal</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>73</v>
+        <v>329</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad Urology and Andrology Hospital</t>
+          <t>Dr Kks uro androcare</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -15369,28 +15349,26 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>632</v>
-      </c>
-      <c r="G45" s="26" t="n">
-        <v>-559</v>
-      </c>
-      <c r="H45" s="26" t="n">
-        <v>0.12</v>
+        <v>354</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>0.93</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J45" s="15" t="n">
-        <v>149</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (632 vs 73)</t>
+          <t>BUILD REVIEWS — Allopathic rival leads 354 vs 329</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +559 to match)</t>
+          <t>Build reviews (need +25 to match)</t>
         </is>
       </c>
     </row>
@@ -15402,357 +15380,357 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Vanasthalipuram</t>
+          <t>Uppal</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Vasanth Poly Clinic</t>
+          <t>DR.ALI'S SEXUAL HEALTH CLINIC</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1459</v>
-      </c>
-      <c r="G46" s="26" t="n">
-        <v>-1386</v>
+        <v>94</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>-77</v>
       </c>
       <c r="H46" s="26" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (1459 vs 73)</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (94 vs 17)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1386 to match)</t>
+          <t>Build reviews (need +77 to match)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>New Palasia</t>
+          <t>Vanasthalipuram</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Dr. Maratha Clinic</t>
+          <t>Sexayush Clinic | Best Sexologist in Hyderabad | Sexual health &amp; STD/STI / SEX Doctor</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>341</v>
-      </c>
-      <c r="G47" s="26" t="n">
-        <v>-340</v>
+        <v>62</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>-37</v>
       </c>
       <c r="H47" s="26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>202</v>
+      </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (341 vs 1)</t>
+          <t>BUILD REVIEWS — Thin rival far ahead (62 vs 25)</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +340 to match)</t>
+          <t>Build reviews (need +37 to match)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Vaishali Nagar</t>
+          <t>New Palasia</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kapil Sharma - Best Psychiatrist in Jaipur | Best Psychologist in Jaipur</t>
+          <t>Dr. Maratha Clinic</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>536</v>
+        <v>341</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>-446</v>
+        <v>-340</v>
       </c>
       <c r="H48" s="26" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J48" s="15" t="n">
-        <v>4280</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (536 vs 90)</t>
+          <t>BUILD REVIEWS — Ayurvedic rival far ahead (341 vs 1)</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +446 to match)</t>
+          <t>Build reviews (need +340 to match)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Vaishali Nagar</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Dr. Maratha Clinic</t>
+          <t>Dr. Jolly Arora - Sexologist in Jaipur, India</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>341</v>
-      </c>
-      <c r="G49" s="26" t="n">
-        <v>-340</v>
-      </c>
-      <c r="H49" s="26" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="G49" s="28" t="n">
+        <v>86</v>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>4.31</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J49" s="15" t="n">
+        <v>4280</v>
+      </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (341 vs 1)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +340 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Gayathri Estates</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Dr Care Homeopathy - Best Homeopathy Clinic in Kurnool, Andhra Pradesh</t>
+          <t>Dr. Maratha Clinic</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Homeopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>507</v>
+        <v>341</v>
       </c>
       <c r="G50" s="26" t="n">
-        <v>-495</v>
+        <v>-340</v>
       </c>
       <c r="H50" s="26" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Homeopathic rival far ahead (507 vs 12)</t>
+          <t>BUILD REVIEWS — Ayurvedic rival far ahead (341 vs 1)</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +495 to match)</t>
+          <t>Build reviews (need +340 to match)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Vashi</t>
+          <t>Gayathri Estates</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>380</v>
+        <v>12</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai</t>
+          <t>Dr Care Homeopathy - Best Homeopathy Clinic in Kurnool, Andhra Pradesh</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Homeopathic</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>624</v>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>-244</v>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>0.61</v>
+        <v>507</v>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>-495</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>0.02</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 624 vs 380</t>
+          <t>BUILD REVIEWS — Homeopathic rival far ahead (507 vs 12)</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +244 to match)</t>
+          <t>Build reviews (need +495 to match)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Falnir Rd</t>
+          <t>Vashi</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>168</v>
+        <v>380</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Dr Khokar</t>
+          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Unani</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>256</v>
+        <v>624</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>-88</v>
+        <v>-244</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>743</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (256 vs 168)</t>
+          <t>BUILD REVIEWS — Allopathic rival leads 624 vs 380</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +88 to match)</t>
+          <t>Build reviews (need +244 to match)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Andheri East</t>
+          <t>Falnir Rd</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>495</v>
+        <v>209</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Dr Sagar Mundada</t>
+          <t>w centre for sexual wellness</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -15761,28 +15739,26 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>788</v>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>-293</v>
-      </c>
-      <c r="H53" s="27" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="G53" s="28" t="n">
+        <v>98</v>
+      </c>
+      <c r="H53" s="28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="15" t="n">
-        <v>908</v>
+        <v>743</v>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 788 vs 495</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +293 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15794,36 +15770,36 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Borivali</t>
+          <t>Andheri East</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>380</v>
+        <v>985</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Dr Anjalika Atrey</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>336</v>
+        <v>569</v>
       </c>
       <c r="G54" s="28" t="n">
-        <v>44</v>
+        <v>416</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>1.13</v>
+        <v>1.73</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>1072</v>
+        <v>908</v>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
@@ -15844,15 +15820,15 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Chembur</t>
+          <t>Borivali</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>495</v>
+        <v>196</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Dr. Aslam Khan Clinic</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -15861,26 +15837,28 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>494</v>
-      </c>
-      <c r="G55" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="28" t="n">
-        <v>1</v>
+        <v>569</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>-373</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0.34</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <v>1072</v>
+      </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 196)</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +373 to match)</t>
         </is>
       </c>
     </row>
@@ -15892,45 +15870,43 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Dadar</t>
+          <t>Chembur</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>382</v>
+        <v>495</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Kaya Kalp International</t>
+          <t>Dr. Aslam Khan Clinic</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>520</v>
-      </c>
-      <c r="G56" s="27" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H56" s="27" t="n">
-        <v>0.73</v>
+        <v>494</v>
+      </c>
+      <c r="G56" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J56" s="15" t="n">
-        <v>1918</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival leads 520 vs 382</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +138 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -15942,15 +15918,15 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Ghatkopar</t>
+          <t>Dadar</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>495</v>
+        <v>318</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Dr. Aslam Khan Clinic</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -15959,28 +15935,28 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>494</v>
-      </c>
-      <c r="G57" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="28" t="n">
-        <v>1</v>
+        <v>569</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>-251</v>
+      </c>
+      <c r="H57" s="27" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>2.7</v>
+        <v>10.7</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>4634</v>
+        <v>1918</v>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Unani rival leads 569 vs 318</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +251 to match)</t>
         </is>
       </c>
     </row>
@@ -15992,45 +15968,45 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Kalyan West</t>
+          <t>Ghatkopar</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Rendezvous With Mind Clinic</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>374</v>
-      </c>
-      <c r="G58" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="H58" s="28" t="n">
-        <v>1.05</v>
+        <v>569</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>0.79</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J58" s="15" t="n">
-        <v>1832</v>
+        <v>4634</v>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (569 vs 449)</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +120 to match)</t>
         </is>
       </c>
     </row>
@@ -16042,45 +16018,45 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Kemps Corner</t>
+          <t>Kalyan West</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>197</v>
+        <v>516</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Sai Krupa Clinic</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>211</v>
+        <v>569</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>-14</v>
+        <v>-53</v>
       </c>
       <c r="H59" s="27" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2.5</v>
+        <v>32.8</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>579</v>
+        <v>1832</v>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival leads 211 vs 197</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (569 vs 516)</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +14 to match)</t>
+          <t>Build reviews (need +53 to match)</t>
         </is>
       </c>
     </row>
@@ -16092,45 +16068,45 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Malad</t>
+          <t>Kemps Corner</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>550</v>
+        <v>111</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Dr Sagar Mundada</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist Specialist in Mumbai</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>361</v>
-      </c>
-      <c r="G60" s="28" t="n">
-        <v>189</v>
-      </c>
-      <c r="H60" s="28" t="n">
-        <v>1.52</v>
+        <v>172</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>-61</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>0.65</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J60" s="15" t="n">
-        <v>2448</v>
+        <v>579</v>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>BUILD REVIEWS — Unani rival leads 172 vs 111</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +61 to match)</t>
         </is>
       </c>
     </row>
@@ -16142,45 +16118,45 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Mira Road</t>
+          <t>Malad</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>4</v>
+        <v>427</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Dr Yogendra Rai</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>7034</v>
-      </c>
-      <c r="G61" s="26" t="n">
-        <v>-7030</v>
-      </c>
-      <c r="H61" s="26" t="n">
-        <v>0</v>
+        <v>569</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H61" s="27" t="n">
+        <v>0.75</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>162</v>
+        <v>2448</v>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (7034 vs 4)</t>
+          <t>BUILD REVIEWS — Unani rival leads 569 vs 427</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +7030 to match)</t>
+          <t>Build reviews (need +142 to match)</t>
         </is>
       </c>
     </row>
@@ -16192,45 +16168,45 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Mulund</t>
+          <t>Mira Road</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Dr. Maratha Clinic | Sexual Health Expert in Ayurveda</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>488</v>
+        <v>569</v>
       </c>
       <c r="G62" s="26" t="n">
-        <v>-478</v>
+        <v>-566</v>
       </c>
       <c r="H62" s="26" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>3.4</v>
+        <v>19.3</v>
       </c>
       <c r="J62" s="15" t="n">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (488 vs 10)</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 3)</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +478 to match)</t>
+          <t>Build reviews (need +566 to match)</t>
         </is>
       </c>
     </row>
@@ -16242,45 +16218,45 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Thane</t>
+          <t>Mulund</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>515</v>
+        <v>8</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vivek Birla</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>545</v>
-      </c>
-      <c r="G63" s="27" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H63" s="27" t="n">
-        <v>0.9399999999999999</v>
+        <v>569</v>
+      </c>
+      <c r="G63" s="26" t="n">
+        <v>-561</v>
+      </c>
+      <c r="H63" s="26" t="n">
+        <v>0.01</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>4.2</v>
+        <v>13.8</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>2146</v>
+        <v>105</v>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 545 vs 515</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 8)</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +30 to match)</t>
+          <t>Build reviews (need +561 to match)</t>
         </is>
       </c>
     </row>
@@ -16292,245 +16268,241 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Vasai</t>
+          <t>Thane</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Dr Suresh Patil Best Psychiatrist &amp; Sexologist in Vasai मनोविकार,सेक्सविकार व व्यसनमुक्ती तज्ञ</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="G64" s="27" t="n">
-        <v>-239</v>
-      </c>
-      <c r="H64" s="26" t="n">
-        <v>0</v>
+        <v>569</v>
+      </c>
+      <c r="G64" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="28" t="n">
+        <v>1.01</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1.5</v>
+        <v>17.8</v>
       </c>
       <c r="J64" s="15" t="n">
-        <v>41</v>
+        <v>2146</v>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (239 vs 0)</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +239 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Saraswathipuram</t>
+          <t>Vasai</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Prerana Psychiatry &amp; Gynaecology Hospital</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>480</v>
-      </c>
-      <c r="G65" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="H65" s="28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>2.1</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="G65" s="26" t="n">
+        <v>-569</v>
+      </c>
+      <c r="H65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="15" t="n">
-        <v>1404</v>
+        <v>41</v>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Winning — hold + keep reviews</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 0)</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>Hold + keep reviews</t>
+          <t>Build reviews (need +569 to match)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Tatya Tope Nagar</t>
+          <t>Saraswathipuram</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>179</v>
+        <v>731</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Krisham Men's Health (Sexology) And Diabetis Clinic</t>
+          <t>Dr Hameed Ibrahim Khokar | Kerala Ayurveda - Sexologist &amp; Infertility Specialist</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1565</v>
-      </c>
-      <c r="G66" s="26" t="n">
-        <v>-1386</v>
-      </c>
-      <c r="H66" s="26" t="n">
-        <v>0.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G66" s="28" t="n">
+        <v>731</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J66" s="15" t="n">
-        <v>531</v>
+        <v>1404</v>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (1565 vs 179)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1386 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Trimurti Chowk</t>
+          <t>Tatya Tope Nagar</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Urja Ayurved Centre</t>
+          <t>Krisham Diabetis and Sexual Wellness Clinic</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>5126</v>
-      </c>
-      <c r="G67" s="26" t="n">
-        <v>-5027</v>
-      </c>
-      <c r="H67" s="26" t="n">
-        <v>0.02</v>
+        <v>270</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H67" s="27" t="n">
+        <v>0.8</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>1547</v>
+        <v>531</v>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Ayurvedic rival far ahead (5126 vs 99)</t>
+          <t>BUILD REVIEWS — Allopathic rival leads 270 vs 217</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +5027 to match)</t>
+          <t>Build reviews (need +53 to match)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Kharghar</t>
+          <t>Trimurti Chowk</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Dr Rahul Bhatambre</t>
+          <t>Dr.NS Ambekar-Female Sexologists</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>525</v>
-      </c>
-      <c r="G68" s="27" t="n">
-        <v>-265</v>
-      </c>
-      <c r="H68" s="26" t="n">
-        <v>0.5</v>
+        <v>124</v>
+      </c>
+      <c r="G68" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="H68" s="28" t="n">
+        <v>1.11</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J68" s="15" t="n">
-        <v>845</v>
+        <v>1547</v>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (525 vs 260)</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +265 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -16542,45 +16514,45 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Panvel</t>
+          <t>Kharghar</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>66</v>
+        <v>186</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Dr Ajinkya Patil</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>655</v>
+        <v>569</v>
       </c>
       <c r="G69" s="26" t="n">
-        <v>-589</v>
+        <v>-383</v>
       </c>
       <c r="H69" s="26" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.9</v>
+        <v>25.9</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>1368</v>
+        <v>845</v>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (655 vs 66)</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 186)</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +589 to match)</t>
+          <t>Build reviews (need +383 to match)</t>
         </is>
       </c>
     </row>
@@ -16592,95 +16564,95 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Vashi</t>
+          <t>Panvel</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>380</v>
+        <v>74</v>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Dr. Vikas Deshmukh - Psychiatrist &amp; Sexologist in Navi Mumbai</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>624</v>
-      </c>
-      <c r="G70" s="27" t="n">
-        <v>-244</v>
-      </c>
-      <c r="H70" s="27" t="n">
-        <v>0.61</v>
+        <v>569</v>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>-495</v>
+      </c>
+      <c r="H70" s="26" t="n">
+        <v>0.13</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1.1</v>
+        <v>31.8</v>
       </c>
       <c r="J70" s="15" t="n">
-        <v>571</v>
+        <v>1368</v>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 624 vs 380</t>
+          <t>BUILD REVIEWS — Unani rival far ahead (569 vs 74)</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +244 to match)</t>
+          <t>Build reviews (need +495 to match)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Navi Mumbai</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Baner</t>
+          <t>Vashi</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Dr. Palash | Urologist &amp; Andrologist Baner Pune</t>
+          <t>Dr. Fayyaz A Sattar | Sexologist in Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Unani</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>248</v>
+        <v>569</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>-167</v>
-      </c>
-      <c r="H71" s="26" t="n">
-        <v>0.33</v>
+        <v>-139</v>
+      </c>
+      <c r="H71" s="27" t="n">
+        <v>0.76</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>0.5</v>
+        <v>16.6</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>1053</v>
+        <v>571</v>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (248 vs 81)</t>
+          <t>BUILD REVIEWS — Unani rival leads 569 vs 430</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +167 to match)</t>
+          <t>Build reviews (need +139 to match)</t>
         </is>
       </c>
     </row>
@@ -16692,45 +16664,45 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Chinchwad</t>
+          <t>Baner</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Yashoda Clinic</t>
+          <t>Dr Erande's | Men &amp; Women’s Sexual Health &amp; Sex Treatment Clinic</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="G72" s="28" t="n">
-        <v>132</v>
-      </c>
-      <c r="H72" s="28" t="n">
-        <v>3.28</v>
+        <v>166</v>
+      </c>
+      <c r="G72" s="27" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H72" s="27" t="n">
+        <v>0.61</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J72" s="15" t="n">
-        <v>697</v>
+        <v>1053</v>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>DEFEND — rank ~#1 but out-reviewed (166 vs 102)</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +64 to match)</t>
         </is>
       </c>
     </row>
@@ -16742,45 +16714,45 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Hadapsar</t>
+          <t>Chinchwad</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>449</v>
+        <v>106</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Kidney And Urology Super Speciality Institute Hospital</t>
+          <t>Dr Erande's | Men &amp; Women’s Sexual Health &amp; Sex Treatment Clinic</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2139</v>
-      </c>
-      <c r="G73" s="26" t="n">
-        <v>-1690</v>
-      </c>
-      <c r="H73" s="26" t="n">
-        <v>0.21</v>
+        <v>170</v>
+      </c>
+      <c r="G73" s="27" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H73" s="27" t="n">
+        <v>0.62</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>2174</v>
+        <v>697</v>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (2139 vs 449)</t>
+          <t>BUILD REVIEWS — Ayurvedic rival leads 170 vs 106</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1690 to match)</t>
+          <t>Build reviews (need +64 to match)</t>
         </is>
       </c>
     </row>
@@ -16792,45 +16764,43 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Katraj</t>
+          <t>Hadapsar</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>130</v>
+        <v>373</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Healing Minds Neuropsychiatry Center</t>
+          <t>Sexologist Dr. Prabhu Vyas</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Non-medical</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="G74" s="27" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H74" s="27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>3.6</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G74" s="28" t="n">
+        <v>345</v>
+      </c>
+      <c r="H74" s="28" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr"/>
       <c r="J74" s="15" t="n">
-        <v>372</v>
+        <v>2174</v>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 242 vs 130</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +112 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
@@ -16842,45 +16812,43 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Kharadi</t>
+          <t>Katraj</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Dr. Kaje Ashirwad Hospital</t>
+          <t>Sexologist Dr. Prabhu Vyas</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Non-medical</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>342</v>
-      </c>
-      <c r="G75" s="27" t="n">
-        <v>-12</v>
-      </c>
-      <c r="H75" s="27" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>0.6</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G75" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="H75" s="28" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="15" t="n">
-        <v>1114</v>
+        <v>372</v>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival leads 342 vs 330</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +12 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -16892,45 +16860,43 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Kothrud</t>
+          <t>Kharadi</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Vanad Clinic</t>
+          <t>Dr Erande's | Men &amp; Women’s Sexual Health &amp; Sex Treatment Clinic</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Homeopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1775</v>
-      </c>
-      <c r="G76" s="26" t="n">
-        <v>-1419</v>
-      </c>
-      <c r="H76" s="26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>5</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G76" s="28" t="n">
+        <v>132</v>
+      </c>
+      <c r="H76" s="28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="15" t="n">
-        <v>1242</v>
+        <v>1114</v>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1775 vs 356)</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1419 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
@@ -16942,213 +16908,211 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Wakad</t>
+          <t>Kothrud</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Dr. Sunil Palve</t>
+          <t>Dr Erande's | Men &amp; Women’s Sexual Health &amp; Sex Treatment Clinic</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>865</v>
-      </c>
-      <c r="G77" s="26" t="n">
-        <v>-560</v>
-      </c>
-      <c r="H77" s="26" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G77" s="28" t="n">
+        <v>130</v>
+      </c>
+      <c r="H77" s="28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr"/>
       <c r="J77" s="15" t="n">
-        <v>1432</v>
+        <v>1242</v>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (865 vs 305)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +560 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Shankar Nagar</t>
+          <t>Wakad</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Dr. Varun Sharma</t>
+          <t>Dr Erande's | Men &amp; Women’s Sexual Health &amp; Sex Treatment Clinic</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="G78" s="27" t="n">
-        <v>-113</v>
-      </c>
-      <c r="H78" s="26" t="n">
-        <v>0.02</v>
+        <v>166</v>
+      </c>
+      <c r="G78" s="28" t="n">
+        <v>97</v>
+      </c>
+      <c r="H78" s="28" t="n">
+        <v>1.58</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J78" s="15" t="n">
-        <v>190</v>
+        <v>1432</v>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (115 vs 2)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +113 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Rajkot</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>University Road</t>
+          <t>Shankar Nagar</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot</t>
+          <t>Dr. Yugendra Chandrakar</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Ayurvedic</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1479</v>
-      </c>
-      <c r="G79" s="26" t="n">
-        <v>-1479</v>
+        <v>30</v>
+      </c>
+      <c r="G79" s="27" t="n">
+        <v>-28</v>
       </c>
       <c r="H79" s="26" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>190</v>
+      </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (1479 vs 0)</t>
+          <t>BUILD REVIEWS — Ayurvedic rival far ahead (30 vs 2)</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1479 to match)</t>
+          <t>Build reviews (need +28 to match)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Rajkot</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Ashok Nagar</t>
+          <t>University Road</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Divya Arogyam Health Clinic - Best Sexologist in Ranchi/Top Sexologist in Ranchi</t>
+          <t>Mind Care Hospital - Dr. Rajesh Ram Psychiatrist in Rajkot | De-Addiction specialist | Sexologist in Rajkot</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Ayurvedic</t>
+          <t>Allopathic</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="G80" s="28" t="n">
-        <v>191</v>
-      </c>
-      <c r="H80" s="28" t="n">
-        <v>1.95</v>
+        <v>1479</v>
+      </c>
+      <c r="G80" s="26" t="n">
+        <v>-1479</v>
+      </c>
+      <c r="H80" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J80" s="15" t="n">
-        <v>728</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
+          <t>BUILD REVIEWS — Allopathic rival far ahead (1479 vs 0)</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>Fix GMB rank/bid (we have reviews)</t>
+          <t>Build reviews (need +1479 to match)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Bhimrad</t>
+          <t>Ashok Nagar</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>33</v>
+        <v>446</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Kalptaru Ayurvedam</t>
+          <t>Divya Arogyam Health Clinic - Best Sexologist in Ranchi/Top Sexologist in Ranchi</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -17157,96 +17121,94 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="G81" s="26" t="n">
-        <v>-673</v>
-      </c>
-      <c r="H81" s="26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>5.6</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G81" s="28" t="n">
+        <v>245</v>
+      </c>
+      <c r="H81" s="28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr"/>
       <c r="J81" s="15" t="n">
-        <v>3372</v>
+        <v>728</v>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (706 vs 33)</t>
+          <t>OUTRANK — we have the reviews, fix GMB/bid</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +673 to match)</t>
+          <t>Fix GMB rank/bid (we have reviews)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Tumkur</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Sira Gate</t>
+          <t>Bhimrad</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Gowri Clinic</t>
+          <t>Raj Clinic Sexologist In Surat</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Allopathic</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" s="27" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H82" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G82" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="H82" s="28" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="15" t="n">
+        <v>3372</v>
+      </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (5 vs 0)</t>
+          <t>Winning — hold + keep reviews</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +5 to match)</t>
+          <t>Hold + keep reviews</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Tumkur</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Alkapuri</t>
+          <t>Sira Gate</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Aashray Urology Institute</t>
+          <t>Gowri Clinic</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -17255,78 +17217,124 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1919</v>
-      </c>
-      <c r="G83" s="26" t="n">
-        <v>-1904</v>
+        <v>5</v>
+      </c>
+      <c r="G83" s="27" t="n">
+        <v>-5</v>
       </c>
       <c r="H83" s="26" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J83" s="15" t="n">
-        <v>332</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>DEFEND — rank ~#1 but out-reviewed (1919 vs 15)</t>
+          <t>BUILD REVIEWS — Allopathic rival far ahead (5 vs 0)</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>Build reviews (need +1904 to match)</t>
+          <t>Build reviews (need +5 to match)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
+          <t>Vadodara</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Alkapuri</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Psychiatrist - Dr. Parth A Soni -Alpha Mind Clinic- Sexologist</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Allopathic</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G84" s="26" t="n">
+        <v>-1185</v>
+      </c>
+      <c r="H84" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J84" s="15" t="n">
+        <v>332</v>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>DEFEND — rank ~#1 but out-reviewed (1200 vs 15)</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Build reviews (need +1185 to match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>MVP Colony</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Dr. M Prasada Rao</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>Allopathic</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>875</v>
-      </c>
-      <c r="G84" s="26" t="n">
-        <v>-834</v>
-      </c>
-      <c r="H84" s="26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J84" s="15" t="n">
+      <c r="C85" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Medikon Sexual Health Care Center - Sex Psychologists | Sexologist | Sex Counselling Doctors in Gajuwaka / Vizag</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Non-medical</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="G85" s="27" t="n">
+        <v>-66</v>
+      </c>
+      <c r="H85" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" s="15" t="n">
         <v>476</v>
       </c>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>BUILD REVIEWS — Allopathic rival far ahead (875 vs 41)</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
-        <is>
-          <t>Build reviews (need +834 to match)</t>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>BUILD REVIEWS — Non-medical rival far ahead (101 vs 35)</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>Build reviews (need +66 to match)</t>
         </is>
       </c>
     </row>
